--- a/Transporteurs/Geodis/Facturation_client.xlsx
+++ b/Transporteurs/Geodis/Facturation_client.xlsx
@@ -10,18 +10,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="346">
   <si>
     <t xml:space="preserve">Dernière exécution : </t>
   </si>
   <si>
-    <t>02/07/2026 13:12:39</t>
+    <t>03/08/2026 08:54:07</t>
   </si>
   <si>
     <t>Date de dernier chargement :</t>
   </si>
   <si>
-    <t>02/07/2026 07:21:30</t>
+    <t>03/08/2026 06:45:45</t>
   </si>
   <si>
     <t>LA RUCHE LOGISTIQUE</t>
@@ -57,7 +57,7 @@
     <t>Poids total(kg) :</t>
   </si>
   <si>
-    <t>2502109369</t>
+    <t>2502109928</t>
   </si>
   <si>
     <t>Extraction des factures</t>
@@ -357,10 +357,7 @@
     <t>Suivi au colis (HT)</t>
   </si>
   <si>
-    <t>LC2 - LIVRAISON SUR CRENEAU HORAIRE  (HT)</t>
-  </si>
-  <si>
-    <t>LCS - LIVRAISON A HEURE DETERMINEE  (HT)</t>
+    <t>MAUT - MAUT (HT)</t>
   </si>
   <si>
     <t>Total CO2eq (kg)</t>
@@ -378,33 +375,99 @@
     <t>001021</t>
   </si>
   <si>
-    <t>2763729</t>
-  </si>
-  <si>
-    <t>93847354</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
+    <t>94320254</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>CX</t>
+  </si>
+  <si>
+    <t>PARC DES EXPOS PARIS LE BOURGET HALL 4 / CARREFOUR CHARLES LINDBERGH</t>
+  </si>
+  <si>
+    <t>- LIVRAISON AVEC TOP H AVANT 11H + APPELER CONTACT</t>
+  </si>
+  <si>
+    <t>VOIE COMMUNALE 4</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>21320</t>
+  </si>
+  <si>
+    <t>CREANCEY</t>
+  </si>
+  <si>
+    <t>STAND PHARMACIE</t>
+  </si>
+  <si>
+    <t>CARREFOUR CHARLES LINDBERGH</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>93350</t>
+  </si>
+  <si>
+    <t>LE BOURGET</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>2816093</t>
+  </si>
+  <si>
+    <t>95599531</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>DU LUNDI AU VENDREDI DE 7H00 / 12H00 MANAGERRECEPTION.CLL@GIPHAR.NET /</t>
+  </si>
+  <si>
+    <t>PASCALE.COUDEYRAS@GIPHAR.NET</t>
+  </si>
+  <si>
+    <t>GIPHAR CASTELNAU-LE-NEZ</t>
+  </si>
+  <si>
+    <t>96 AV CLEMENT ADER</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>34170</t>
+  </si>
+  <si>
+    <t>CASTELNAU LE LEZ</t>
+  </si>
+  <si>
+    <t>EQUIPEMENT</t>
+  </si>
+  <si>
+    <t>2828727</t>
+  </si>
+  <si>
+    <t>95761019</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>MES</t>
   </si>
   <si>
-    <t>VOIE COMMUNALE 4</t>
-  </si>
-  <si>
-    <t>FR</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>21320</t>
-  </si>
-  <si>
-    <t>CREANCEY</t>
-  </si>
-  <si>
     <t>ATIDA OMNIPHAR 07</t>
   </si>
   <si>
@@ -420,46 +483,358 @@
     <t>MONTRABE</t>
   </si>
   <si>
+    <t>2831220</t>
+  </si>
+  <si>
+    <t>96000733</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2831222</t>
+  </si>
+  <si>
+    <t>96001425</t>
+  </si>
+  <si>
+    <t>DU LUNDI AU VENDREDI 07H30-12H30</t>
+  </si>
+  <si>
+    <t>GIPHAR ANGERS</t>
+  </si>
+  <si>
+    <t>RUE ROLAND MORENO</t>
+  </si>
+  <si>
+    <t>P.ACT ANGERS/ATLANTIQUE</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>49170</t>
+  </si>
+  <si>
+    <t>ST LEGER DES BOIS</t>
+  </si>
+  <si>
+    <t>2831219</t>
+  </si>
+  <si>
+    <t>95998500</t>
+  </si>
+  <si>
+    <t>DU LUNDI AU VENDREDI DE 07H30 / 12H30     CONTACT :  CHRISTOPHE THERY</t>
+  </si>
+  <si>
+    <t>/ 0380820745  CHRISTOPHE.THERY@GIPHAR.NET</t>
+  </si>
+  <si>
+    <t>GIPHAR OUGES</t>
+  </si>
+  <si>
+    <t>165 RUE DE L'INNOVATION</t>
+  </si>
+  <si>
+    <t>21600</t>
+  </si>
+  <si>
+    <t>OUGES</t>
+  </si>
+  <si>
+    <t>2831351</t>
+  </si>
+  <si>
+    <t>96001096</t>
+  </si>
+  <si>
+    <t>DU LUNDI AU VENDREDI DE 08H15-12H00 / 13H00-17H15</t>
+  </si>
+  <si>
+    <t>GIPHAR GRANVILLIER</t>
+  </si>
+  <si>
+    <t>42 RUE HYACINTHE PETIT</t>
+  </si>
+  <si>
+    <t>GROSSISTE/REPART</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>60210</t>
+  </si>
+  <si>
+    <t>GRANDVILLIERS</t>
+  </si>
+  <si>
+    <t>BDC83448</t>
+  </si>
+  <si>
+    <t>96043464</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>ENTRE 9 ET 11H.</t>
+  </si>
+  <si>
+    <t>PARAPHARMACIE AUCHAN OSNY</t>
+  </si>
+  <si>
+    <t>CHE DU POIRIER CHARLES GUERIN</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>95520</t>
+  </si>
+  <si>
+    <t>OSNY</t>
+  </si>
+  <si>
+    <t>BDC83462</t>
+  </si>
+  <si>
+    <t>96043989</t>
+  </si>
+  <si>
+    <t>ENTRE 9 ET 11H</t>
+  </si>
+  <si>
+    <t>AUCHAN MANTES</t>
+  </si>
+  <si>
+    <t>RTE DEPARTEMENTALE 110</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>78200</t>
+  </si>
+  <si>
+    <t>BUCHELAY</t>
+  </si>
+  <si>
+    <t>2840052</t>
+  </si>
+  <si>
+    <t>96075792</t>
+  </si>
+  <si>
+    <t>HORAIRE DE LIVRAISON : 08H30-12H00 DU LUNDI AU JEUDI PAS DE LIVRAISON</t>
+  </si>
+  <si>
+    <t>LE VENDREDI.</t>
+  </si>
+  <si>
+    <t>INFLIGHT SALES</t>
+  </si>
+  <si>
+    <t>3 RUE DES FRERES THONET</t>
+  </si>
+  <si>
+    <t>PARC DES ENTREPRENEURS</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>94450</t>
+  </si>
+  <si>
+    <t>LIMEIL BREVANNES</t>
+  </si>
+  <si>
+    <t>446923</t>
+  </si>
+  <si>
+    <t>EXP20260630-2829577</t>
+  </si>
+  <si>
+    <t>96169868</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>LES LIVRAISONS SE FONT SUR RENDEZ-VOUS AU 03.52.15.37.33 AVANT 13H DU</t>
+  </si>
+  <si>
+    <t>LUNDI AU VENDREDI</t>
+  </si>
+  <si>
+    <t>FABRIQUE DE STYLES CORMONTREUIL</t>
+  </si>
+  <si>
+    <t>11 RUE DES LAPS ZA LES PARQUES</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>51350</t>
+  </si>
+  <si>
+    <t>CORMONTREUIL</t>
+  </si>
+  <si>
+    <t>BAG OF COFFEE</t>
+  </si>
+  <si>
+    <t>2842217</t>
+  </si>
+  <si>
+    <t>96232624</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2840313</t>
+  </si>
+  <si>
+    <t>96253315</t>
+  </si>
+  <si>
+    <t>LIVRAISON AVEC PRISE DE RDV OBLIGATOIRE AU 06.81.26.30.89 / LOGISTIQUE</t>
+  </si>
+  <si>
+    <t>FRANCE@REDCARE-PHARMACY.COM</t>
+  </si>
+  <si>
+    <t>REDCARE PHARMACY</t>
+  </si>
+  <si>
+    <t>4 RUE DU CHAUFFOUR</t>
+  </si>
+  <si>
+    <t>HYGEE SANTE PA DE LA BROYE</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>59710</t>
+  </si>
+  <si>
+    <t>ENNEVELIN</t>
+  </si>
+  <si>
+    <t>999941885855</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>AFF</t>
+  </si>
+  <si>
+    <t>PAS DE SEMI</t>
+  </si>
+  <si>
+    <t>BWC MEDIA V2VIN</t>
+  </si>
+  <si>
+    <t>2 ALL. DES ISATIS</t>
+  </si>
+  <si>
+    <t>SERVICE EXPÉDITION</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>33700</t>
+  </si>
+  <si>
+    <t>MERIGNAC</t>
+  </si>
+  <si>
+    <t>2842332</t>
+  </si>
+  <si>
+    <t>84258</t>
+  </si>
+  <si>
+    <t>96368056</t>
+  </si>
+  <si>
+    <t>PRISE DE RDV : HTTPS://ESSENTIELS-PHARMA.FR/PRISE-DE-RENDEZ-VOUS/LUNDI</t>
+  </si>
+  <si>
+    <t>AU VENDREDI DE 7H A 10H30</t>
+  </si>
+  <si>
+    <t>ESSENTIELS PHARMA</t>
+  </si>
+  <si>
+    <t>1 RUE DE L'ARDELIERE</t>
+  </si>
+  <si>
+    <t>49070</t>
+  </si>
+  <si>
+    <t>BEAUCOUZE</t>
+  </si>
+  <si>
+    <t>2843141</t>
+  </si>
+  <si>
+    <t>96413483</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>PARC INDUSTRIEL DE LA PLAINE DE L'AIN</t>
+  </si>
+  <si>
+    <t>VEEPEE</t>
+  </si>
+  <si>
+    <t>ALL FIGUE ET LIEVRE</t>
+  </si>
+  <si>
+    <t>LYON 3 MANHATTAN</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>01150</t>
+  </si>
+  <si>
+    <t>ST VULBAS</t>
+  </si>
+  <si>
     <t>EQUIPEMENTS</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>2766395</t>
-  </si>
-  <si>
-    <t>94081655</t>
-  </si>
-  <si>
-    <t>2026-06-02</t>
-  </si>
-  <si>
-    <t>2766417</t>
-  </si>
-  <si>
-    <t>94231593</t>
-  </si>
-  <si>
-    <t>2026-06-03</t>
-  </si>
-  <si>
-    <t>CX</t>
-  </si>
-  <si>
-    <t>PRENDRE RDV AVEC M. CHADER (RDV OBLIGATOIRE POUR LA LIVRAISON): M. CHA</t>
-  </si>
-  <si>
-    <t>DER TEL+33 (0)6 69 98 42 58E-MAIL : MCHADER@MALONGO.COM</t>
-  </si>
-  <si>
-    <t>CMC MALONGO LOGISTIQUE</t>
-  </si>
-  <si>
-    <t>1ERE AVENUE - 2EME RUE</t>
-  </si>
-  <si>
-    <t>PORTAIL N 2</t>
+    <t>2836001</t>
+  </si>
+  <si>
+    <t>96430222</t>
+  </si>
+  <si>
+    <t>PRISE DE RDV OBLIGATOIRE TEL 0685119484-0631875898- MAIL:C.VALLEE@TRAN</t>
+  </si>
+  <si>
+    <t>SCAN.FR</t>
+  </si>
+  <si>
+    <t>EASY PARAPHARMACIE</t>
+  </si>
+  <si>
+    <t>DEPOT N  7 1ERE AVENUE</t>
+  </si>
+  <si>
+    <t>TRANSCAN 4789</t>
   </si>
   <si>
     <t>06</t>
@@ -471,670 +846,190 @@
     <t>CARROS</t>
   </si>
   <si>
-    <t>999941488288</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>AFF</t>
-  </si>
-  <si>
-    <t>JE REVIENS POUR L HEURE DE RDV</t>
-  </si>
-  <si>
-    <t>SAMADA (BÂTIMENT PROLOGIS)</t>
-  </si>
-  <si>
-    <t>1754 AVENUE PAUL DELOUVRIER</t>
-  </si>
-  <si>
-    <t>PARK MOISSY 2 LES CHEVRONS PORTE J</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>77550</t>
-  </si>
-  <si>
-    <t>MOISSY CRAMAYEL</t>
-  </si>
-  <si>
-    <t>000093630935</t>
-  </si>
-  <si>
-    <t>2757138</t>
-  </si>
-  <si>
-    <t>999941536885</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>ENL</t>
-  </si>
-  <si>
-    <t>RESTITUTION D'expédition 000093630935</t>
-  </si>
-  <si>
-    <t>RETOUR CERP RRM</t>
-  </si>
-  <si>
-    <t>Z.A.C. DE L'ANJOLY</t>
-  </si>
-  <si>
-    <t>VOIE D'IRLANDE</t>
+    <t>2844748</t>
+  </si>
+  <si>
+    <t>96564612</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2857433</t>
+  </si>
+  <si>
+    <t>96690698</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2849362</t>
+  </si>
+  <si>
+    <t>96704080</t>
+  </si>
+  <si>
+    <t>N DE COMMANDE : FBC978295 RDV /WWW.SHIPT.IO/SLOTIFY/ALLTRICKSBRUYÈRE</t>
+  </si>
+  <si>
+    <t>CONFIRMATION RDV TEL: 0130485285</t>
+  </si>
+  <si>
+    <t>ALLTRICKS FRANCE</t>
+  </si>
+  <si>
+    <t>10 RUE DE LA BRUYERE</t>
+  </si>
+  <si>
+    <t>AVANIS ALLTRICKS</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>28200</t>
+  </si>
+  <si>
+    <t>CHATEAUDUN</t>
+  </si>
+  <si>
+    <t>2857409</t>
+  </si>
+  <si>
+    <t>96837628</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>VENTE-PRIVEECOM</t>
+  </si>
+  <si>
+    <t>PARC INDUSTRIEL LA PLAINE DE L'AIN</t>
+  </si>
+  <si>
+    <t>ALLEE FIGUES ET LIEVRES</t>
+  </si>
+  <si>
+    <t>2861359</t>
+  </si>
+  <si>
+    <t>96867278</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2861329</t>
+  </si>
+  <si>
+    <t>96869634</t>
+  </si>
+  <si>
+    <t>2861322</t>
+  </si>
+  <si>
+    <t>96869933</t>
+  </si>
+  <si>
+    <t>2868959</t>
+  </si>
+  <si>
+    <t>96987111</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>999942011149</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>BIEN SE PRÉSENTER AC BL ET CMR MENTIONNANT L'EXPÉDITEUR, DESTINATAIRE</t>
+  </si>
+  <si>
+    <t>FINAL, PAYS DE DESTINATION : CRVM GUADELOUPE RDV LE : MARDI 28/07</t>
+  </si>
+  <si>
+    <t>BALGUERIE OUTRE P/C CRVM GUADELOUPE</t>
+  </si>
+  <si>
+    <t>BRANGEON TRANSPORT ET LOG</t>
+  </si>
+  <si>
+    <t>49 ROUTE DE L'INDUSTRIE</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>27210</t>
+  </si>
+  <si>
+    <t>ST MACLOU</t>
+  </si>
+  <si>
+    <t>2869321</t>
+  </si>
+  <si>
+    <t>97295204</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>MEI</t>
+  </si>
+  <si>
+    <t>NORDBERLINER WERKGEMEINSCHAFT GGMBH</t>
+  </si>
+  <si>
+    <t>TRIFTSTRASSE 36</t>
+  </si>
+  <si>
+    <t>DE</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>13400</t>
-  </si>
-  <si>
-    <t>AUBAGNE</t>
-  </si>
-  <si>
-    <t>94320254</t>
-  </si>
-  <si>
-    <t>PARC DES EXPOS PARIS LE BOURGET HALL 4 / CARREFOUR CHARLES LINDBERGH</t>
-  </si>
-  <si>
-    <t>- LIVRAISON AVEC TOP H AVANT 11H + APPELER CONTACT</t>
-  </si>
-  <si>
-    <t>STAND PHARMACIE</t>
-  </si>
-  <si>
-    <t>CARREFOUR CHARLES LINDBERGH</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>93350</t>
-  </si>
-  <si>
-    <t>LE BOURGET</t>
-  </si>
-  <si>
-    <t>2781238</t>
-  </si>
-  <si>
-    <t>BDC79432</t>
-  </si>
-  <si>
-    <t>94380676</t>
-  </si>
-  <si>
-    <t>PRISE DE RDV : HTTPS://ESSENTIELS-PHARMA.FR/PRISE-DE-RENDEZ-VOUS/LUNDI</t>
-  </si>
-  <si>
-    <t>AU VENDREDI DE 7H A 10H30</t>
-  </si>
-  <si>
-    <t>ESSENTIELS PHARMA</t>
-  </si>
-  <si>
-    <t>1 RUE DE L'ARDELIERE</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>49070</t>
-  </si>
-  <si>
-    <t>BEAUCOUZE</t>
-  </si>
-  <si>
-    <t>2782347</t>
-  </si>
-  <si>
-    <t>94431027</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>PRISE DE RDV OBLIGATOIRE TEL 0685119484-0631875898- MAIL:C.VALLEE@TRAN</t>
-  </si>
-  <si>
-    <t>SCAN.FR</t>
-  </si>
-  <si>
-    <t>EASY PARAPHARMACIE</t>
-  </si>
-  <si>
-    <t>DEPOT N  7 1ERE AVENUE</t>
-  </si>
-  <si>
-    <t>TRANSCAN 4789</t>
-  </si>
-  <si>
-    <t>2778926</t>
-  </si>
-  <si>
-    <t>94433083</t>
-  </si>
-  <si>
-    <t>N DE COMMANDE : FBC974244 N D'ACCORD DE LIVRAISON : PPS260603020 PRI</t>
-  </si>
-  <si>
-    <t>SE DE RDV: HTTPS://WWW.SHIPT.IO/SLOTIFY/ALLTRICKSBRUYERE / TEL: 013048</t>
-  </si>
-  <si>
-    <t>ALLTRICKS FRANCE</t>
-  </si>
-  <si>
-    <t>10 RUE DE LA BRUYERE</t>
-  </si>
-  <si>
-    <t>AVANIS ALLTRICKS</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>28200</t>
-  </si>
-  <si>
-    <t>CHATEAUDUN</t>
-  </si>
-  <si>
-    <t>2774798</t>
-  </si>
-  <si>
-    <t>94464606</t>
-  </si>
-  <si>
-    <t>DHYGIETAL</t>
-  </si>
-  <si>
-    <t>1 RUE DE LA NAU DES VIGNES</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>51520</t>
-  </si>
-  <si>
-    <t>LA VEUVE</t>
-  </si>
-  <si>
-    <t>HYD06260008</t>
-  </si>
-  <si>
-    <t>999941517742</t>
-  </si>
-  <si>
-    <t>2026-06-09</t>
-  </si>
-  <si>
-    <t>LIV IMPERATIVE LE 11/06 ENTRE 6 ET 8H00</t>
-  </si>
-  <si>
-    <t>ENTREPÔT SAMADA</t>
-  </si>
-  <si>
-    <t>PARC DU HAUT DE WISSOUS 2</t>
-  </si>
-  <si>
-    <t>CHEMIN DE LA CROIX BRISÉE (QUAI 153</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>91320</t>
-  </si>
-  <si>
-    <t>WISSOUS</t>
-  </si>
-  <si>
-    <t>2777656</t>
-  </si>
-  <si>
-    <t>94291375</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>AFG</t>
-  </si>
-  <si>
-    <t>B2B PHARMA</t>
-  </si>
-  <si>
-    <t>11 RUE DES FONDEURS</t>
-  </si>
-  <si>
-    <t>ENTREPOT TRIGNAC - ZA ALTITUDE</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>44570</t>
-  </si>
-  <si>
-    <t>TRIGNAC</t>
-  </si>
-  <si>
-    <t>999941565971</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
+    <t>13127</t>
+  </si>
+  <si>
+    <t>BERLIN</t>
+  </si>
+  <si>
+    <t>DAP</t>
+  </si>
+  <si>
+    <t>999942011785</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
   </si>
   <si>
     <t>ERD</t>
   </si>
   <si>
-    <t>NUTRILIQ BY FORENA</t>
-  </si>
-  <si>
-    <t>VLAANDERENLAAN 27</t>
-  </si>
-  <si>
-    <t>BE</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>8970</t>
-  </si>
-  <si>
-    <t>POPERINGE</t>
+    <t>ITALIA PRO</t>
+  </si>
+  <si>
+    <t>VIA L.MANZONI</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>31015</t>
+  </si>
+  <si>
+    <t>CONEGLIANO</t>
   </si>
   <si>
     <t>EXW</t>
-  </si>
-  <si>
-    <t>2792629</t>
-  </si>
-  <si>
-    <t>94806618</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>BDC2026061180462</t>
-  </si>
-  <si>
-    <t>2792712</t>
-  </si>
-  <si>
-    <t>94851743</t>
-  </si>
-  <si>
-    <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>2798843</t>
-  </si>
-  <si>
-    <t>94906944</t>
-  </si>
-  <si>
-    <t>LAGARDERE TRAVEL RETAIL FCE</t>
-  </si>
-  <si>
-    <t>7 RUE JEAN JAURES</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>95670</t>
-  </si>
-  <si>
-    <t>MARLY LA VILLE</t>
-  </si>
-  <si>
-    <t>999941668167</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>M&amp;M MILITZER &amp; MÜNCH</t>
-  </si>
-  <si>
-    <t>19 ALLÉE DU CLOS DE CHARMES</t>
-  </si>
-  <si>
-    <t>77090</t>
-  </si>
-  <si>
-    <t>COLLEGIEN</t>
-  </si>
-  <si>
-    <t>EXP20260615-2799804</t>
-  </si>
-  <si>
-    <t>440823</t>
-  </si>
-  <si>
-    <t>95104244</t>
-  </si>
-  <si>
-    <t>2805970</t>
-  </si>
-  <si>
-    <t>95191602</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>2806998</t>
-  </si>
-  <si>
-    <t>BDC2026061881351</t>
-  </si>
-  <si>
-    <t>95325743</t>
-  </si>
-  <si>
-    <t>2026-06-23</t>
-  </si>
-  <si>
-    <t>HORAIRE DE LIVRAISON : 08H30-12H00 DU LUNDI AU JEUDI PAS DE LIVRAISON</t>
-  </si>
-  <si>
-    <t>LE VENDREDI.</t>
-  </si>
-  <si>
-    <t>INFLIGHT SALES</t>
-  </si>
-  <si>
-    <t>3 RUE DES FRERES THONET</t>
-  </si>
-  <si>
-    <t>PARC DES ENTREPRENEURS</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>94450</t>
-  </si>
-  <si>
-    <t>LIMEIL BREVANNES</t>
-  </si>
-  <si>
-    <t>2805267</t>
-  </si>
-  <si>
-    <t>95334322</t>
-  </si>
-  <si>
-    <t>2813733</t>
-  </si>
-  <si>
-    <t>95392225</t>
-  </si>
-  <si>
-    <t>EQUIPEMENT</t>
-  </si>
-  <si>
-    <t>EXP20260624-2815943</t>
-  </si>
-  <si>
-    <t>95455892</t>
-  </si>
-  <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
-    <t>MEI</t>
-  </si>
-  <si>
-    <t>LE TRANSPORTEUR DOIT RESERVER LE CRENEAU DE DECHARGEMENT A L'ENTREPOT</t>
-  </si>
-  <si>
-    <t>SUR LE PORTAIL SUIVANT : HTTPS://I-RS.RIVALTASPED.NET/</t>
-  </si>
-  <si>
-    <t>WAREHOUSE RS 2.0 TORRE GAROFOLI</t>
-  </si>
-  <si>
-    <t>STRADA COMUNALE BOSCO SNC</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>15057</t>
-  </si>
-  <si>
-    <t>TORTONA</t>
-  </si>
-  <si>
-    <t>DAP</t>
-  </si>
-  <si>
-    <t>999941756837</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>SARL MAJ</t>
-  </si>
-  <si>
-    <t>5 BOULEVARD EIFFEL</t>
-  </si>
-  <si>
-    <t>21600</t>
-  </si>
-  <si>
-    <t>2816095</t>
-  </si>
-  <si>
-    <t>95496289</t>
-  </si>
-  <si>
-    <t>2813873</t>
-  </si>
-  <si>
-    <t>B2B11235</t>
-  </si>
-  <si>
-    <t>95591735</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>RETAIL CONCEPTS NV</t>
-  </si>
-  <si>
-    <t>SMALLANDLAAN 9</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>2660</t>
-  </si>
-  <si>
-    <t>HOBOKEN (ANTWERPEN)</t>
-  </si>
-  <si>
-    <t>2815946</t>
-  </si>
-  <si>
-    <t>95597955</t>
-  </si>
-  <si>
-    <t>DU LUNDI AU VENDREDI DE 08H15-12H00 / 13H00-17H15 CONTACT : SEBASTIEN</t>
-  </si>
-  <si>
-    <t>BLACOT / 0344464397 SEBASTIEN.BLECOT@GIPHAR.NET</t>
-  </si>
-  <si>
-    <t>GROSSISTE/REPART</t>
-  </si>
-  <si>
-    <t>42 RUE HYACINTHE PETIT</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>60210</t>
-  </si>
-  <si>
-    <t>GRANDVILLIERS</t>
-  </si>
-  <si>
-    <t>2819400</t>
-  </si>
-  <si>
-    <t>95600280</t>
-  </si>
-  <si>
-    <t>DU LUNDI AU VENDREDI 07H30-12H30 CONTACT : STEPHANIE LANNOY / 02413114</t>
-  </si>
-  <si>
-    <t>71 MNAGERRECEPTION.ANG@GIPHAR.NET</t>
-  </si>
-  <si>
-    <t>GIPHAR ANGERS</t>
-  </si>
-  <si>
-    <t>RUE ROLAND MORENO</t>
-  </si>
-  <si>
-    <t>49170</t>
-  </si>
-  <si>
-    <t>ST LEGER DES BOIS</t>
-  </si>
-  <si>
-    <t>BDC-20260624-82069</t>
-  </si>
-  <si>
-    <t>95596160</t>
-  </si>
-  <si>
-    <t>DU LUNDI AU VENDREDI DE 07H30 / 12H30     CONTACT :  CHRISTOPHE THERY</t>
-  </si>
-  <si>
-    <t>/ 0380820745  CHRISTOPHE.THERY@GIPHAR.NET</t>
-  </si>
-  <si>
-    <t>GIPHAR OUGES</t>
-  </si>
-  <si>
-    <t>165 RUE DE L'INNOVATION</t>
-  </si>
-  <si>
-    <t>OUGES</t>
-  </si>
-  <si>
-    <t>2816093</t>
-  </si>
-  <si>
-    <t>95599531</t>
-  </si>
-  <si>
-    <t>DU LUNDI AU VENDREDI DE 7H00 / 12H00 MANAGERRECEPTION.CLL@GIPHAR.NET /</t>
-  </si>
-  <si>
-    <t>PASCALE.COUDEYRAS@GIPHAR.NET</t>
-  </si>
-  <si>
-    <t>GIPHAR CASTELNAU-LE-NEZ</t>
-  </si>
-  <si>
-    <t>96 AV CLEMENT ADER</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>34170</t>
-  </si>
-  <si>
-    <t>CASTELNAU LE LEZ</t>
-  </si>
-  <si>
-    <t>EXP20260622-2812231</t>
-  </si>
-  <si>
-    <t>95602040</t>
-  </si>
-  <si>
-    <t>SOFIA COSMETIQUES</t>
-  </si>
-  <si>
-    <t>ZI 1ERE AVENUE, 4E RUE</t>
-  </si>
-  <si>
-    <t>2818456</t>
-  </si>
-  <si>
-    <t>BDC2026062582274</t>
-  </si>
-  <si>
-    <t>95686648</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>95732649</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>CELLUSA</t>
-  </si>
-  <si>
-    <t>1 PLACE DE LA LOGISTIQUE</t>
-  </si>
-  <si>
-    <t>SOGARIS-BAT S-Q2</t>
-  </si>
-  <si>
-    <t>94150</t>
-  </si>
-  <si>
-    <t>RUNGIS</t>
-  </si>
-  <si>
-    <t>2813677</t>
-  </si>
-  <si>
-    <t>95756330</t>
-  </si>
-  <si>
-    <t>ENTREPOT SAMADA</t>
-  </si>
-  <si>
-    <t>2 CHEMIN DE LA CROIX BRISEE</t>
-  </si>
-  <si>
-    <t>PARC DU HAUT DE WISSOUS</t>
-  </si>
-  <si>
-    <t>2828727</t>
-  </si>
-  <si>
-    <t>95761019</t>
   </si>
   <si>
     <t>Pied de facture - Facturation client</t>
@@ -1584,26 +1479,26 @@
         <v>15</v>
       </c>
       <c r="B14" s="9">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C14" s="10">
-        <v>6481.95</v>
+        <v>6010.2</v>
       </c>
       <c r="D14" s="10">
-        <v>1296.39</v>
+        <v>1202.04</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="10">
-        <v>7778.34</v>
+        <v>7212.24</v>
       </c>
       <c r="G14" s="10">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H14" s="10">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I14" s="10">
-        <v>15501.6</v>
+        <v>4612.075</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
@@ -1627,7 +1522,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CR40"/>
+  <dimension ref="A1:CQ33"/>
   <cols>
     <col min="1" max="4" width="12.9789" customWidth="1"/>
     <col min="5" max="5" width="26.6685" customWidth="1"/>
@@ -1642,8 +1537,8 @@
     <col min="29" max="33" width="12.9789" customWidth="1"/>
     <col min="34" max="34" width="15.03234" customWidth="1"/>
     <col min="35" max="37" width="12.9789" customWidth="1"/>
-    <col min="38" max="96" width="15.03234" customWidth="1"/>
-    <col min="97" max="97" width="4.67767866666667" customWidth="1"/>
+    <col min="38" max="95" width="15.03234" customWidth="1"/>
+    <col min="96" max="96" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="58.1297" customHeight="1">
@@ -1744,7 +1639,6 @@
       <c r="CO1" s="15"/>
       <c r="CP1" s="15"/>
       <c r="CQ1" s="15"/>
-      <c r="CR1" s="15"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="54.9299" customHeight="1">
       <c r="A2" s="16"/>
@@ -1842,7 +1736,6 @@
       <c r="CO2" s="17"/>
       <c r="CP2" s="17"/>
       <c r="CQ2" s="17"/>
-      <c r="CR2" s="17"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="54.9299" customHeight="1">
       <c r="A3" s="18" t="s">
@@ -1945,12 +1838,11 @@
       <c r="CN3" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="CO3" s="19"/>
-      <c r="CP3" s="19" t="s">
+      <c r="CO3" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="CQ3" s="19"/>
-      <c r="CR3" s="19" t="s">
+      <c r="CP3" s="19"/>
+      <c r="CQ3" s="19" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2240,19 +2132,16 @@
       <c r="CQ4" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="CR4" s="19" t="s">
-        <v>119</v>
-      </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="18.1322" customHeight="1">
       <c r="A5" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>6</v>
@@ -2261,23 +2150,27 @@
         <v>4</v>
       </c>
       <c r="F5" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G5" s="20" t="s">
         <v>121</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>122</v>
       </c>
       <c r="H5" s="20"/>
       <c r="I5" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="K5" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="J5" s="20" t="s">
+      <c r="L5" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="K5" s="20" t="s">
+      <c r="M5" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
       <c r="N5" s="20" t="s">
         <v>4</v>
       </c>
@@ -2316,17 +2209,15 @@
       <c r="AA5" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="AB5" s="20" t="s">
-        <v>136</v>
-      </c>
+      <c r="AB5" s="20"/>
       <c r="AC5" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD5" s="22">
-        <v>32</v>
+        <v>17.7</v>
       </c>
       <c r="AE5" s="22">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="AF5" s="22">
         <v>0</v>
@@ -2344,18 +2235,18 @@
       <c r="AK5" s="20"/>
       <c r="AL5" s="22"/>
       <c r="AM5" s="22">
-        <v>5.7</v>
+        <v>41.32</v>
       </c>
       <c r="AN5" s="22">
-        <v>5.7</v>
+        <v>41.32</v>
       </c>
       <c r="AO5" s="22"/>
       <c r="AP5" s="22"/>
       <c r="AQ5" s="22">
-        <v>1.18</v>
+        <v>8.26</v>
       </c>
       <c r="AR5" s="22">
-        <v>6.88</v>
+        <v>49.58</v>
       </c>
       <c r="AS5" s="22"/>
       <c r="AT5" s="22">
@@ -2365,7 +2256,9 @@
       <c r="AV5" s="22"/>
       <c r="AW5" s="20"/>
       <c r="AX5" s="22"/>
-      <c r="AY5" s="22"/>
+      <c r="AY5" s="22">
+        <v>41.32</v>
+      </c>
       <c r="AZ5" s="22"/>
       <c r="BA5" s="22"/>
       <c r="BB5" s="22"/>
@@ -2385,9 +2278,7 @@
       <c r="BP5" s="22"/>
       <c r="BQ5" s="22"/>
       <c r="BR5" s="22"/>
-      <c r="BS5" s="22">
-        <v>5.7</v>
-      </c>
+      <c r="BS5" s="22"/>
       <c r="BT5" s="22"/>
       <c r="BU5" s="22"/>
       <c r="BV5" s="22"/>
@@ -2409,26 +2300,23 @@
       <c r="CL5" s="22"/>
       <c r="CM5" s="22"/>
       <c r="CN5" s="23"/>
-      <c r="CO5" s="23"/>
+      <c r="CO5" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP5" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ5" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR5" s="22">
-        <v>32</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="CQ5" s="22"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="18.1322" customHeight="1">
       <c r="A6" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>6</v>
@@ -2437,23 +2325,27 @@
         <v>4</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H6" s="20"/>
       <c r="I6" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="J6" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="J6" s="20" t="s">
+      <c r="K6" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L6" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="K6" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="M6" s="20" t="s">
+        <v>141</v>
+      </c>
       <c r="N6" s="20" t="s">
         <v>4</v>
       </c>
@@ -2474,33 +2366,35 @@
         <v>130</v>
       </c>
       <c r="U6" s="20" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="V6" s="20" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="W6" s="20"/>
       <c r="X6" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y6" s="20" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="Z6" s="20" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="AA6" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="AB6" s="20"/>
+        <v>146</v>
+      </c>
+      <c r="AB6" s="20" t="s">
+        <v>147</v>
+      </c>
       <c r="AC6" s="22">
         <v>1</v>
       </c>
       <c r="AD6" s="22">
-        <v>44</v>
+        <v>174.5</v>
       </c>
       <c r="AE6" s="22">
-        <v>44</v>
+        <v>174.5</v>
       </c>
       <c r="AF6" s="22">
         <v>0</v>
@@ -2516,26 +2410,20 @@
         <v>0</v>
       </c>
       <c r="AK6" s="20"/>
-      <c r="AL6" s="22">
-        <v>39.8</v>
-      </c>
+      <c r="AL6" s="22"/>
       <c r="AM6" s="22">
-        <v>5.7</v>
+        <v>135</v>
       </c>
       <c r="AN6" s="22">
-        <v>45.5</v>
-      </c>
-      <c r="AO6" s="22">
-        <v>6.81</v>
-      </c>
-      <c r="AP6" s="22">
-        <v>2.6</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="AO6" s="22"/>
+      <c r="AP6" s="22"/>
       <c r="AQ6" s="22">
-        <v>10.98</v>
+        <v>27</v>
       </c>
       <c r="AR6" s="22">
-        <v>65.89</v>
+        <v>162</v>
       </c>
       <c r="AS6" s="22"/>
       <c r="AT6" s="22">
@@ -2544,7 +2432,9 @@
       <c r="AU6" s="22"/>
       <c r="AV6" s="22"/>
       <c r="AW6" s="20"/>
-      <c r="AX6" s="22"/>
+      <c r="AX6" s="22">
+        <v>135</v>
+      </c>
       <c r="AY6" s="22"/>
       <c r="AZ6" s="22"/>
       <c r="BA6" s="22"/>
@@ -2565,9 +2455,7 @@
       <c r="BP6" s="22"/>
       <c r="BQ6" s="22"/>
       <c r="BR6" s="22"/>
-      <c r="BS6" s="22">
-        <v>5.7</v>
-      </c>
+      <c r="BS6" s="22"/>
       <c r="BT6" s="22"/>
       <c r="BU6" s="22"/>
       <c r="BV6" s="22"/>
@@ -2589,15 +2477,14 @@
       <c r="CL6" s="22"/>
       <c r="CM6" s="22"/>
       <c r="CN6" s="22"/>
-      <c r="CO6" s="22"/>
+      <c r="CO6" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP6" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ6" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR6" s="22">
-        <v>44</v>
+        <v>136</v>
+      </c>
+      <c r="CQ6" s="22">
+        <v>180</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2605,10 +2492,10 @@
         <v>15</v>
       </c>
       <c r="B7" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>6</v>
@@ -2617,27 +2504,23 @@
         <v>4</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H7" s="20"/>
       <c r="I7" s="20" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="K7" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="L7" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="M7" s="20" t="s">
-        <v>146</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
       <c r="N7" s="20" t="s">
         <v>4</v>
       </c>
@@ -2658,37 +2541,33 @@
         <v>130</v>
       </c>
       <c r="U7" s="20" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="V7" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="W7" s="20" t="s">
-        <v>149</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="W7" s="20"/>
       <c r="X7" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y7" s="20" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="Z7" s="20" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="AA7" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB7" s="20" t="s">
-        <v>136</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="AB7" s="20"/>
       <c r="AC7" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD7" s="22">
-        <v>28</v>
+        <v>35.5</v>
       </c>
       <c r="AE7" s="22">
-        <v>28</v>
+        <v>35.5</v>
       </c>
       <c r="AF7" s="22">
         <v>0</v>
@@ -2704,24 +2583,20 @@
         <v>0</v>
       </c>
       <c r="AK7" s="20"/>
-      <c r="AL7" s="22">
-        <v>107.4</v>
-      </c>
-      <c r="AM7" s="22"/>
+      <c r="AL7" s="22"/>
+      <c r="AM7" s="22">
+        <v>5.7</v>
+      </c>
       <c r="AN7" s="22">
-        <v>107.4</v>
-      </c>
-      <c r="AO7" s="22">
-        <v>18.37</v>
-      </c>
-      <c r="AP7" s="22">
-        <v>2.6</v>
-      </c>
+        <v>5.7</v>
+      </c>
+      <c r="AO7" s="22"/>
+      <c r="AP7" s="22"/>
       <c r="AQ7" s="22">
-        <v>25.67</v>
+        <v>1.14</v>
       </c>
       <c r="AR7" s="22">
-        <v>154.04</v>
+        <v>6.84</v>
       </c>
       <c r="AS7" s="22"/>
       <c r="AT7" s="22">
@@ -2751,7 +2626,9 @@
       <c r="BP7" s="22"/>
       <c r="BQ7" s="22"/>
       <c r="BR7" s="22"/>
-      <c r="BS7" s="22"/>
+      <c r="BS7" s="22">
+        <v>5.7</v>
+      </c>
       <c r="BT7" s="22"/>
       <c r="BU7" s="22"/>
       <c r="BV7" s="22"/>
@@ -2773,15 +2650,14 @@
       <c r="CL7" s="22"/>
       <c r="CM7" s="22"/>
       <c r="CN7" s="23"/>
-      <c r="CO7" s="23"/>
+      <c r="CO7" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP7" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ7" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR7" s="22">
-        <v>28</v>
+        <v>136</v>
+      </c>
+      <c r="CQ7" s="22">
+        <v>36</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -2789,10 +2665,10 @@
         <v>15</v>
       </c>
       <c r="B8" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>6</v>
@@ -2801,23 +2677,27 @@
         <v>4</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G8" s="20"/>
+        <v>120</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>157</v>
+      </c>
       <c r="H8" s="20"/>
       <c r="I8" s="20" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="K8" s="20" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="L8" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="M8" s="20"/>
+        <v>140</v>
+      </c>
+      <c r="M8" s="20" t="s">
+        <v>141</v>
+      </c>
       <c r="N8" s="20" t="s">
         <v>4</v>
       </c>
@@ -2838,35 +2718,33 @@
         <v>130</v>
       </c>
       <c r="U8" s="20" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="V8" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="W8" s="20" t="s">
-        <v>159</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="W8" s="20"/>
       <c r="X8" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y8" s="20" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="Z8" s="20" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="AA8" s="20" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="AB8" s="20"/>
       <c r="AC8" s="22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD8" s="22">
-        <v>343</v>
+        <v>228.5</v>
       </c>
       <c r="AE8" s="22">
-        <v>343</v>
+        <v>228.5</v>
       </c>
       <c r="AF8" s="22">
         <v>0</v>
@@ -2876,30 +2754,32 @@
       </c>
       <c r="AH8" s="22"/>
       <c r="AI8" s="22">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="22">
         <v>0</v>
       </c>
       <c r="AK8" s="20"/>
       <c r="AL8" s="22">
-        <v>292.76</v>
-      </c>
-      <c r="AM8" s="22"/>
+        <v>278.84</v>
+      </c>
+      <c r="AM8" s="22">
+        <v>180</v>
+      </c>
       <c r="AN8" s="22">
-        <v>292.76</v>
+        <v>458.84</v>
       </c>
       <c r="AO8" s="22">
-        <v>20.49</v>
+        <v>45.7</v>
       </c>
       <c r="AP8" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ8" s="22">
-        <v>63.17</v>
+        <v>101.43</v>
       </c>
       <c r="AR8" s="22">
-        <v>379.02</v>
+        <v>608.57</v>
       </c>
       <c r="AS8" s="22"/>
       <c r="AT8" s="22">
@@ -2909,7 +2789,9 @@
       <c r="AV8" s="22"/>
       <c r="AW8" s="20"/>
       <c r="AX8" s="22"/>
-      <c r="AY8" s="22"/>
+      <c r="AY8" s="22">
+        <v>180</v>
+      </c>
       <c r="AZ8" s="22"/>
       <c r="BA8" s="22"/>
       <c r="BB8" s="22"/>
@@ -2951,24 +2833,23 @@
       <c r="CL8" s="22"/>
       <c r="CM8" s="22"/>
       <c r="CN8" s="22"/>
-      <c r="CO8" s="22"/>
+      <c r="CO8" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP8" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ8" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR8" s="22"/>
+        <v>136</v>
+      </c>
+      <c r="CQ8" s="22"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="18.1322" customHeight="1">
       <c r="A9" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>6</v>
@@ -2977,78 +2858,74 @@
         <v>4</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>164</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="H9" s="20"/>
       <c r="I9" s="20" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K9" s="20" t="s">
-        <v>167</v>
+        <v>123</v>
       </c>
       <c r="L9" s="20" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="M9" s="20"/>
       <c r="N9" s="20" t="s">
-        <v>169</v>
+        <v>4</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="P9" s="20" t="s">
-        <v>171</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="P9" s="20"/>
       <c r="Q9" s="20" t="s">
         <v>127</v>
       </c>
       <c r="R9" s="20" t="s">
-        <v>172</v>
+        <v>128</v>
       </c>
       <c r="S9" s="20" t="s">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="T9" s="20" t="s">
-        <v>174</v>
+        <v>130</v>
       </c>
       <c r="U9" s="20" t="s">
-        <v>4</v>
+        <v>163</v>
       </c>
       <c r="V9" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="W9" s="20"/>
+        <v>164</v>
+      </c>
+      <c r="W9" s="20" t="s">
+        <v>165</v>
+      </c>
       <c r="X9" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y9" s="20" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="Z9" s="20" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="AA9" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB9" s="20" t="s">
-        <v>136</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="AB9" s="20"/>
       <c r="AC9" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD9" s="22">
-        <v>8.7</v>
+        <v>437</v>
       </c>
       <c r="AE9" s="22">
-        <v>8.7</v>
+        <v>437</v>
       </c>
       <c r="AF9" s="22">
         <v>0</v>
@@ -3065,23 +2942,25 @@
       </c>
       <c r="AK9" s="20"/>
       <c r="AL9" s="22">
-        <v>54.48</v>
-      </c>
-      <c r="AM9" s="22"/>
+        <v>266.72</v>
+      </c>
+      <c r="AM9" s="22">
+        <v>190</v>
+      </c>
       <c r="AN9" s="22">
-        <v>54.48</v>
+        <v>456.72</v>
       </c>
       <c r="AO9" s="22">
-        <v>9.32</v>
+        <v>43.72</v>
       </c>
       <c r="AP9" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ9" s="22">
-        <v>13.28</v>
+        <v>100.6</v>
       </c>
       <c r="AR9" s="22">
-        <v>79.68</v>
+        <v>603.64</v>
       </c>
       <c r="AS9" s="22"/>
       <c r="AT9" s="22">
@@ -3091,7 +2970,9 @@
       <c r="AV9" s="22"/>
       <c r="AW9" s="20"/>
       <c r="AX9" s="22"/>
-      <c r="AY9" s="22"/>
+      <c r="AY9" s="22">
+        <v>190</v>
+      </c>
       <c r="AZ9" s="22"/>
       <c r="BA9" s="22"/>
       <c r="BB9" s="22"/>
@@ -3133,26 +3014,23 @@
       <c r="CL9" s="22"/>
       <c r="CM9" s="22"/>
       <c r="CN9" s="23"/>
-      <c r="CO9" s="23"/>
+      <c r="CO9" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP9" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ9" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR9" s="22">
-        <v>9</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="CQ9" s="22"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="18.1322" customHeight="1">
       <c r="A10" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>6</v>
@@ -3161,26 +3039,26 @@
         <v>4</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="H10" s="20"/>
       <c r="I10" s="20" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="J10" s="20" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K10" s="20" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="L10" s="20" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="M10" s="20" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="N10" s="20" t="s">
         <v>4</v>
@@ -3202,33 +3080,33 @@
         <v>130</v>
       </c>
       <c r="U10" s="20" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="V10" s="20" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="W10" s="20"/>
       <c r="X10" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y10" s="20" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="Z10" s="20" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="AA10" s="20" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="AB10" s="20"/>
       <c r="AC10" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD10" s="22">
-        <v>17.7</v>
+        <v>177</v>
       </c>
       <c r="AE10" s="22">
-        <v>18</v>
+        <v>177</v>
       </c>
       <c r="AF10" s="22">
         <v>0</v>
@@ -3245,25 +3123,25 @@
       </c>
       <c r="AK10" s="20"/>
       <c r="AL10" s="22">
-        <v>55.1</v>
+        <v>54.83</v>
       </c>
       <c r="AM10" s="22">
-        <v>76.2</v>
+        <v>150</v>
       </c>
       <c r="AN10" s="22">
-        <v>131.3</v>
+        <v>204.83</v>
       </c>
       <c r="AO10" s="22">
-        <v>9.42</v>
+        <v>8.99</v>
       </c>
       <c r="AP10" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ10" s="22">
-        <v>28.66</v>
+        <v>43.29</v>
       </c>
       <c r="AR10" s="22">
-        <v>171.98</v>
+        <v>259.71</v>
       </c>
       <c r="AS10" s="22"/>
       <c r="AT10" s="22">
@@ -3273,16 +3151,16 @@
       <c r="AV10" s="22"/>
       <c r="AW10" s="20"/>
       <c r="AX10" s="22"/>
-      <c r="AY10" s="22"/>
+      <c r="AY10" s="22">
+        <v>150</v>
+      </c>
       <c r="AZ10" s="22"/>
       <c r="BA10" s="22"/>
       <c r="BB10" s="22"/>
       <c r="BC10" s="22"/>
       <c r="BD10" s="22"/>
       <c r="BE10" s="22"/>
-      <c r="BF10" s="22">
-        <v>9.9</v>
-      </c>
+      <c r="BF10" s="22"/>
       <c r="BG10" s="22"/>
       <c r="BH10" s="22"/>
       <c r="BI10" s="22"/>
@@ -3317,26 +3195,23 @@
       <c r="CL10" s="22"/>
       <c r="CM10" s="22"/>
       <c r="CN10" s="22"/>
-      <c r="CO10" s="22">
-        <v>66.3</v>
+      <c r="CO10" s="20" t="s">
+        <v>136</v>
       </c>
       <c r="CP10" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ10" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR10" s="22"/>
+        <v>136</v>
+      </c>
+      <c r="CQ10" s="22"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="18.1322" customHeight="1">
       <c r="A11" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>6</v>
@@ -3345,29 +3220,25 @@
         <v>4</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>184</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="H11" s="20"/>
       <c r="I11" s="20" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K11" s="20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="L11" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="M11" s="20" t="s">
-        <v>187</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="M11" s="20"/>
       <c r="N11" s="20" t="s">
         <v>4</v>
       </c>
@@ -3388,33 +3259,35 @@
         <v>130</v>
       </c>
       <c r="U11" s="20" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="V11" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="W11" s="20"/>
+        <v>181</v>
+      </c>
+      <c r="W11" s="20" t="s">
+        <v>182</v>
+      </c>
       <c r="X11" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y11" s="20" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="Z11" s="20" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="AA11" s="20" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="AB11" s="20"/>
       <c r="AC11" s="22">
         <v>1</v>
       </c>
       <c r="AD11" s="22">
-        <v>170</v>
+        <v>312</v>
       </c>
       <c r="AE11" s="22">
-        <v>170</v>
+        <v>312</v>
       </c>
       <c r="AF11" s="22">
         <v>0</v>
@@ -3431,25 +3304,23 @@
       </c>
       <c r="AK11" s="20"/>
       <c r="AL11" s="22">
-        <v>89.64</v>
-      </c>
-      <c r="AM11" s="22">
-        <v>5.7</v>
-      </c>
+        <v>335.07</v>
+      </c>
+      <c r="AM11" s="22"/>
       <c r="AN11" s="22">
-        <v>95.34</v>
+        <v>335.07</v>
       </c>
       <c r="AO11" s="22">
-        <v>15.33</v>
+        <v>54.92</v>
       </c>
       <c r="AP11" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ11" s="22">
-        <v>22.66</v>
+        <v>78.51</v>
       </c>
       <c r="AR11" s="22">
-        <v>135.93</v>
+        <v>471.1</v>
       </c>
       <c r="AS11" s="22"/>
       <c r="AT11" s="22">
@@ -3479,9 +3350,7 @@
       <c r="BP11" s="22"/>
       <c r="BQ11" s="22"/>
       <c r="BR11" s="22"/>
-      <c r="BS11" s="22">
-        <v>5.7</v>
-      </c>
+      <c r="BS11" s="22"/>
       <c r="BT11" s="22"/>
       <c r="BU11" s="22"/>
       <c r="BV11" s="22"/>
@@ -3503,26 +3372,23 @@
       <c r="CL11" s="22"/>
       <c r="CM11" s="22"/>
       <c r="CN11" s="23"/>
-      <c r="CO11" s="23"/>
+      <c r="CO11" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP11" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ11" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR11" s="22">
-        <v>170</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="CQ11" s="22"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="18.1322" customHeight="1">
       <c r="A12" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>6</v>
@@ -3531,27 +3397,25 @@
         <v>4</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="H12" s="20"/>
       <c r="I12" s="20" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="K12" s="20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="L12" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="M12" s="20" t="s">
-        <v>197</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="M12" s="20"/>
       <c r="N12" s="20" t="s">
         <v>4</v>
       </c>
@@ -3572,35 +3436,33 @@
         <v>130</v>
       </c>
       <c r="U12" s="20" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="V12" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="W12" s="20" t="s">
-        <v>200</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="W12" s="20"/>
       <c r="X12" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y12" s="20" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="Z12" s="20" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="AA12" s="20" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="AB12" s="20"/>
       <c r="AC12" s="22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD12" s="22">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AE12" s="22">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AF12" s="22">
         <v>0</v>
@@ -3617,25 +3479,25 @@
       </c>
       <c r="AK12" s="20"/>
       <c r="AL12" s="22">
-        <v>32.25</v>
+        <v>61.79</v>
       </c>
       <c r="AM12" s="22">
-        <v>5.7</v>
+        <v>23.7</v>
       </c>
       <c r="AN12" s="22">
-        <v>37.95</v>
+        <v>85.49</v>
       </c>
       <c r="AO12" s="22">
-        <v>5.51</v>
+        <v>10.13</v>
       </c>
       <c r="AP12" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ12" s="22">
-        <v>9.21</v>
+        <v>19.65</v>
       </c>
       <c r="AR12" s="22">
-        <v>55.27</v>
+        <v>117.87</v>
       </c>
       <c r="AS12" s="22"/>
       <c r="AT12" s="22">
@@ -3652,9 +3514,15 @@
       <c r="BC12" s="22"/>
       <c r="BD12" s="22"/>
       <c r="BE12" s="22"/>
-      <c r="BF12" s="22"/>
-      <c r="BG12" s="22"/>
-      <c r="BH12" s="22"/>
+      <c r="BF12" s="22">
+        <v>9.9</v>
+      </c>
+      <c r="BG12" s="22">
+        <v>10.7</v>
+      </c>
+      <c r="BH12" s="22">
+        <v>3.1</v>
+      </c>
       <c r="BI12" s="22"/>
       <c r="BJ12" s="22"/>
       <c r="BK12" s="22"/>
@@ -3665,9 +3533,7 @@
       <c r="BP12" s="22"/>
       <c r="BQ12" s="22"/>
       <c r="BR12" s="22"/>
-      <c r="BS12" s="22">
-        <v>5.7</v>
-      </c>
+      <c r="BS12" s="22"/>
       <c r="BT12" s="22"/>
       <c r="BU12" s="22"/>
       <c r="BV12" s="22"/>
@@ -3689,15 +3555,14 @@
       <c r="CL12" s="22"/>
       <c r="CM12" s="22"/>
       <c r="CN12" s="22"/>
-      <c r="CO12" s="22"/>
+      <c r="CO12" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP12" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ12" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR12" s="22">
-        <v>21</v>
+        <v>136</v>
+      </c>
+      <c r="CQ12" s="22">
+        <v>10</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -3705,10 +3570,10 @@
         <v>15</v>
       </c>
       <c r="B13" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>6</v>
@@ -3717,27 +3582,25 @@
         <v>4</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="H13" s="20"/>
       <c r="I13" s="20" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="K13" s="20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="L13" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="M13" s="20" t="s">
-        <v>204</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="M13" s="20"/>
       <c r="N13" s="20" t="s">
         <v>4</v>
       </c>
@@ -3758,37 +3621,33 @@
         <v>130</v>
       </c>
       <c r="U13" s="20" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="V13" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="W13" s="20" t="s">
-        <v>207</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="W13" s="20"/>
       <c r="X13" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y13" s="20" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="Z13" s="20" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="AA13" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="AB13" s="20" t="s">
-        <v>136</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="AB13" s="20"/>
       <c r="AC13" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD13" s="22">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AE13" s="22">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AF13" s="22">
         <v>0</v>
@@ -3805,25 +3664,25 @@
       </c>
       <c r="AK13" s="20"/>
       <c r="AL13" s="22">
-        <v>17.86</v>
+        <v>36.74</v>
       </c>
       <c r="AM13" s="22">
-        <v>5.7</v>
+        <v>13</v>
       </c>
       <c r="AN13" s="22">
-        <v>23.56</v>
+        <v>49.74</v>
       </c>
       <c r="AO13" s="22">
-        <v>3.05</v>
+        <v>6.02</v>
       </c>
       <c r="AP13" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ13" s="22">
-        <v>5.84</v>
+        <v>11.67</v>
       </c>
       <c r="AR13" s="22">
-        <v>35.05</v>
+        <v>70.03</v>
       </c>
       <c r="AS13" s="22"/>
       <c r="AT13" s="22">
@@ -3840,9 +3699,13 @@
       <c r="BC13" s="22"/>
       <c r="BD13" s="22"/>
       <c r="BE13" s="22"/>
-      <c r="BF13" s="22"/>
+      <c r="BF13" s="22">
+        <v>9.9</v>
+      </c>
       <c r="BG13" s="22"/>
-      <c r="BH13" s="22"/>
+      <c r="BH13" s="22">
+        <v>3.1</v>
+      </c>
       <c r="BI13" s="22"/>
       <c r="BJ13" s="22"/>
       <c r="BK13" s="22"/>
@@ -3853,9 +3716,7 @@
       <c r="BP13" s="22"/>
       <c r="BQ13" s="22"/>
       <c r="BR13" s="22"/>
-      <c r="BS13" s="22">
-        <v>5.7</v>
-      </c>
+      <c r="BS13" s="22"/>
       <c r="BT13" s="22"/>
       <c r="BU13" s="22"/>
       <c r="BV13" s="22"/>
@@ -3877,26 +3738,23 @@
       <c r="CL13" s="22"/>
       <c r="CM13" s="22"/>
       <c r="CN13" s="23"/>
-      <c r="CO13" s="23"/>
+      <c r="CO13" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP13" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ13" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR13" s="22">
-        <v>8</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="CQ13" s="22"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="18.1322" customHeight="1">
       <c r="A14" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D14" s="20" t="s">
         <v>6</v>
@@ -3905,23 +3763,27 @@
         <v>4</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="H14" s="20"/>
       <c r="I14" s="20" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="J14" s="20" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="K14" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="L14" s="20"/>
-      <c r="M14" s="20"/>
+        <v>151</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="M14" s="20" t="s">
+        <v>206</v>
+      </c>
       <c r="N14" s="20" t="s">
         <v>4</v>
       </c>
@@ -3942,35 +3804,35 @@
         <v>130</v>
       </c>
       <c r="U14" s="20" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="V14" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="W14" s="20"/>
+        <v>208</v>
+      </c>
+      <c r="W14" s="20" t="s">
+        <v>209</v>
+      </c>
       <c r="X14" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y14" s="20" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="Z14" s="20" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="AA14" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="AB14" s="20" t="s">
-        <v>136</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="AB14" s="20"/>
       <c r="AC14" s="22">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AD14" s="22">
-        <v>80</v>
+        <v>106.5</v>
       </c>
       <c r="AE14" s="22">
-        <v>80</v>
+        <v>106.5</v>
       </c>
       <c r="AF14" s="22">
         <v>0</v>
@@ -3987,23 +3849,25 @@
       </c>
       <c r="AK14" s="20"/>
       <c r="AL14" s="22">
-        <v>38.94</v>
-      </c>
-      <c r="AM14" s="22"/>
+        <v>54.21</v>
+      </c>
+      <c r="AM14" s="22">
+        <v>9.9</v>
+      </c>
       <c r="AN14" s="22">
-        <v>38.94</v>
+        <v>64.11</v>
       </c>
       <c r="AO14" s="22">
-        <v>6.66</v>
+        <v>8.89</v>
       </c>
       <c r="AP14" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ14" s="22">
-        <v>9.64</v>
+        <v>15.12</v>
       </c>
       <c r="AR14" s="22">
-        <v>57.84</v>
+        <v>90.72</v>
       </c>
       <c r="AS14" s="22"/>
       <c r="AT14" s="22">
@@ -4020,7 +3884,9 @@
       <c r="BC14" s="22"/>
       <c r="BD14" s="22"/>
       <c r="BE14" s="22"/>
-      <c r="BF14" s="22"/>
+      <c r="BF14" s="22">
+        <v>9.9</v>
+      </c>
       <c r="BG14" s="22"/>
       <c r="BH14" s="22"/>
       <c r="BI14" s="22"/>
@@ -4055,15 +3921,14 @@
       <c r="CL14" s="22"/>
       <c r="CM14" s="22"/>
       <c r="CN14" s="22"/>
-      <c r="CO14" s="22"/>
+      <c r="CO14" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP14" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ14" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR14" s="22">
-        <v>80</v>
+        <v>136</v>
+      </c>
+      <c r="CQ14" s="22">
+        <v>110</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -4071,10 +3936,10 @@
         <v>15</v>
       </c>
       <c r="B15" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>6</v>
@@ -4083,25 +3948,29 @@
         <v>4</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G15" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="M15" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="J15" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="K15" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="L15" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="M15" s="20"/>
       <c r="N15" s="20" t="s">
         <v>4</v>
       </c>
@@ -4122,35 +3991,35 @@
         <v>130</v>
       </c>
       <c r="U15" s="20" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="V15" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="W15" s="20" t="s">
-        <v>224</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="W15" s="20"/>
       <c r="X15" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y15" s="20" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="Z15" s="20" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="AA15" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="AB15" s="20"/>
+        <v>223</v>
+      </c>
+      <c r="AB15" s="20" t="s">
+        <v>224</v>
+      </c>
       <c r="AC15" s="22">
         <v>1</v>
       </c>
       <c r="AD15" s="22">
-        <v>132</v>
+        <v>10</v>
       </c>
       <c r="AE15" s="22">
-        <v>132</v>
+        <v>10</v>
       </c>
       <c r="AF15" s="22">
         <v>0</v>
@@ -4160,30 +4029,32 @@
       </c>
       <c r="AH15" s="22"/>
       <c r="AI15" s="22">
-        <v>400000e-6</v>
+        <v>0</v>
       </c>
       <c r="AJ15" s="22">
         <v>0</v>
       </c>
       <c r="AK15" s="20"/>
       <c r="AL15" s="22">
-        <v>120.52</v>
-      </c>
-      <c r="AM15" s="22"/>
+        <v>17.65</v>
+      </c>
+      <c r="AM15" s="22">
+        <v>5.7</v>
+      </c>
       <c r="AN15" s="22">
-        <v>120.52</v>
+        <v>23.35</v>
       </c>
       <c r="AO15" s="22">
-        <v>8.44</v>
+        <v>2.89</v>
       </c>
       <c r="AP15" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ15" s="22">
-        <v>26.31</v>
+        <v>5.77</v>
       </c>
       <c r="AR15" s="22">
-        <v>157.87</v>
+        <v>34.61</v>
       </c>
       <c r="AS15" s="22"/>
       <c r="AT15" s="22">
@@ -4213,7 +4084,9 @@
       <c r="BP15" s="22"/>
       <c r="BQ15" s="22"/>
       <c r="BR15" s="22"/>
-      <c r="BS15" s="22"/>
+      <c r="BS15" s="22">
+        <v>5.7</v>
+      </c>
       <c r="BT15" s="22"/>
       <c r="BU15" s="22"/>
       <c r="BV15" s="22"/>
@@ -4235,24 +4108,25 @@
       <c r="CL15" s="22"/>
       <c r="CM15" s="22"/>
       <c r="CN15" s="23"/>
-      <c r="CO15" s="23"/>
+      <c r="CO15" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP15" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ15" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR15" s="22"/>
+        <v>136</v>
+      </c>
+      <c r="CQ15" s="22">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="18.1322" customHeight="1">
       <c r="A16" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>6</v>
@@ -4261,20 +4135,20 @@
         <v>4</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H16" s="20"/>
       <c r="I16" s="20" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J16" s="20" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>231</v>
+        <v>151</v>
       </c>
       <c r="L16" s="20"/>
       <c r="M16" s="20"/>
@@ -4298,37 +4172,33 @@
         <v>130</v>
       </c>
       <c r="U16" s="20" t="s">
-        <v>232</v>
+        <v>152</v>
       </c>
       <c r="V16" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="W16" s="20" t="s">
-        <v>234</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="W16" s="20"/>
       <c r="X16" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y16" s="20" t="s">
-        <v>235</v>
+        <v>154</v>
       </c>
       <c r="Z16" s="20" t="s">
-        <v>236</v>
+        <v>155</v>
       </c>
       <c r="AA16" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="AB16" s="20" t="s">
-        <v>136</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="AB16" s="20"/>
       <c r="AC16" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD16" s="22">
-        <v>437</v>
+        <v>52.5</v>
       </c>
       <c r="AE16" s="22">
-        <v>437</v>
+        <v>52.5</v>
       </c>
       <c r="AF16" s="22">
         <v>0</v>
@@ -4345,23 +4215,23 @@
       </c>
       <c r="AK16" s="20"/>
       <c r="AL16" s="22">
-        <v>137.46</v>
+        <v>43.58</v>
       </c>
       <c r="AM16" s="22"/>
       <c r="AN16" s="22">
-        <v>137.46</v>
+        <v>43.58</v>
       </c>
       <c r="AO16" s="22">
-        <v>23.51</v>
+        <v>7.14</v>
       </c>
       <c r="AP16" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ16" s="22">
-        <v>32.71</v>
+        <v>10.67</v>
       </c>
       <c r="AR16" s="22">
-        <v>196.28</v>
+        <v>63.99</v>
       </c>
       <c r="AS16" s="22"/>
       <c r="AT16" s="22">
@@ -4413,15 +4283,14 @@
       <c r="CL16" s="22"/>
       <c r="CM16" s="22"/>
       <c r="CN16" s="22"/>
-      <c r="CO16" s="22"/>
+      <c r="CO16" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP16" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ16" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR16" s="22">
-        <v>2</v>
+        <v>136</v>
+      </c>
+      <c r="CQ16" s="22">
+        <v>53</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -4429,10 +4298,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>6</v>
@@ -4441,68 +4310,76 @@
         <v>4</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G17" s="20"/>
+        <v>120</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>228</v>
+      </c>
       <c r="H17" s="20"/>
       <c r="I17" s="20" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
+        <v>151</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="M17" s="20" t="s">
+        <v>231</v>
+      </c>
       <c r="N17" s="20" t="s">
-        <v>241</v>
+        <v>4</v>
       </c>
       <c r="O17" s="20" t="s">
-        <v>242</v>
+        <v>126</v>
       </c>
       <c r="P17" s="20"/>
       <c r="Q17" s="20" t="s">
-        <v>243</v>
+        <v>127</v>
       </c>
       <c r="R17" s="20" t="s">
-        <v>244</v>
+        <v>128</v>
       </c>
       <c r="S17" s="20" t="s">
-        <v>245</v>
+        <v>129</v>
       </c>
       <c r="T17" s="20" t="s">
-        <v>246</v>
+        <v>130</v>
       </c>
       <c r="U17" s="20" t="s">
-        <v>4</v>
+        <v>232</v>
       </c>
       <c r="V17" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="W17" s="20"/>
+        <v>233</v>
+      </c>
+      <c r="W17" s="20" t="s">
+        <v>234</v>
+      </c>
       <c r="X17" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y17" s="20" t="s">
-        <v>128</v>
+        <v>235</v>
       </c>
       <c r="Z17" s="20" t="s">
-        <v>129</v>
+        <v>236</v>
       </c>
       <c r="AA17" s="20" t="s">
-        <v>130</v>
+        <v>237</v>
       </c>
       <c r="AB17" s="20"/>
       <c r="AC17" s="22">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AD17" s="22">
-        <v>1289</v>
+        <v>68</v>
       </c>
       <c r="AE17" s="22">
-        <v>1289</v>
+        <v>68</v>
       </c>
       <c r="AF17" s="22">
         <v>0</v>
@@ -4512,30 +4389,32 @@
       </c>
       <c r="AH17" s="22"/>
       <c r="AI17" s="22">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AJ17" s="22">
         <v>0</v>
       </c>
       <c r="AK17" s="20"/>
       <c r="AL17" s="22">
-        <v>433</v>
-      </c>
-      <c r="AM17" s="22"/>
+        <v>42.08</v>
+      </c>
+      <c r="AM17" s="22">
+        <v>25.6</v>
+      </c>
       <c r="AN17" s="22">
-        <v>433</v>
+        <v>67.68</v>
       </c>
       <c r="AO17" s="22">
-        <v>30.31</v>
+        <v>6.9</v>
       </c>
       <c r="AP17" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ17" s="22">
-        <v>93.18</v>
+        <v>15.44</v>
       </c>
       <c r="AR17" s="22">
-        <v>559.09</v>
+        <v>92.62</v>
       </c>
       <c r="AS17" s="22"/>
       <c r="AT17" s="22">
@@ -4543,9 +4422,7 @@
       </c>
       <c r="AU17" s="22"/>
       <c r="AV17" s="22"/>
-      <c r="AW17" s="20" t="s">
-        <v>247</v>
-      </c>
+      <c r="AW17" s="20"/>
       <c r="AX17" s="22"/>
       <c r="AY17" s="22"/>
       <c r="AZ17" s="22"/>
@@ -4555,7 +4432,9 @@
       <c r="BD17" s="22"/>
       <c r="BE17" s="22"/>
       <c r="BF17" s="22"/>
-      <c r="BG17" s="22"/>
+      <c r="BG17" s="22">
+        <v>19.9</v>
+      </c>
       <c r="BH17" s="22"/>
       <c r="BI17" s="22"/>
       <c r="BJ17" s="22"/>
@@ -4567,7 +4446,9 @@
       <c r="BP17" s="22"/>
       <c r="BQ17" s="22"/>
       <c r="BR17" s="22"/>
-      <c r="BS17" s="22"/>
+      <c r="BS17" s="22">
+        <v>5.7</v>
+      </c>
       <c r="BT17" s="22"/>
       <c r="BU17" s="22"/>
       <c r="BV17" s="22"/>
@@ -4589,24 +4470,25 @@
       <c r="CL17" s="22"/>
       <c r="CM17" s="22"/>
       <c r="CN17" s="23"/>
-      <c r="CO17" s="23"/>
+      <c r="CO17" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP17" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ17" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR17" s="22"/>
+        <v>136</v>
+      </c>
+      <c r="CQ17" s="22">
+        <v>68</v>
+      </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18.1322" customHeight="1">
       <c r="A18" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D18" s="20" t="s">
         <v>6</v>
@@ -4615,22 +4497,22 @@
         <v>4</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>248</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G18" s="20"/>
       <c r="H18" s="20"/>
       <c r="I18" s="20" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="J18" s="20" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="K18" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="L18" s="20"/>
+        <v>240</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>241</v>
+      </c>
       <c r="M18" s="20"/>
       <c r="N18" s="20" t="s">
         <v>4</v>
@@ -4652,35 +4534,35 @@
         <v>130</v>
       </c>
       <c r="U18" s="20" t="s">
-        <v>131</v>
+        <v>242</v>
       </c>
       <c r="V18" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="W18" s="20"/>
+        <v>243</v>
+      </c>
+      <c r="W18" s="20" t="s">
+        <v>244</v>
+      </c>
       <c r="X18" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y18" s="20" t="s">
-        <v>133</v>
+        <v>245</v>
       </c>
       <c r="Z18" s="20" t="s">
-        <v>134</v>
+        <v>246</v>
       </c>
       <c r="AA18" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="AB18" s="20" t="s">
-        <v>136</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="AB18" s="20"/>
       <c r="AC18" s="22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD18" s="22">
-        <v>47</v>
+        <v>671</v>
       </c>
       <c r="AE18" s="22">
-        <v>47</v>
+        <v>671</v>
       </c>
       <c r="AF18" s="22">
         <v>0</v>
@@ -4688,34 +4570,32 @@
       <c r="AG18" s="22">
         <v>0</v>
       </c>
-      <c r="AH18" s="22">
-        <v>9.8</v>
-      </c>
+      <c r="AH18" s="22"/>
       <c r="AI18" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ18" s="22">
         <v>0</v>
       </c>
       <c r="AK18" s="20"/>
       <c r="AL18" s="22">
-        <v>39.8</v>
+        <v>363.93</v>
       </c>
       <c r="AM18" s="22"/>
       <c r="AN18" s="22">
-        <v>39.8</v>
+        <v>363.93</v>
       </c>
       <c r="AO18" s="22">
-        <v>6.81</v>
+        <v>25.47</v>
       </c>
       <c r="AP18" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ18" s="22">
-        <v>11.8</v>
+        <v>78.4</v>
       </c>
       <c r="AR18" s="22">
-        <v>70.81</v>
+        <v>470.4</v>
       </c>
       <c r="AS18" s="22"/>
       <c r="AT18" s="22">
@@ -4767,26 +4647,23 @@
       <c r="CL18" s="22"/>
       <c r="CM18" s="22"/>
       <c r="CN18" s="22"/>
-      <c r="CO18" s="22"/>
+      <c r="CO18" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP18" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ18" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR18" s="22">
-        <v>47</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="CQ18" s="22"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="18.1322" customHeight="1">
       <c r="A19" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>6</v>
@@ -4795,28 +4672,28 @@
         <v>4</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G19" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="L19" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="H19" s="20" t="s">
+      <c r="M19" s="20" t="s">
         <v>252</v>
-      </c>
-      <c r="I19" s="20" t="s">
-        <v>253</v>
-      </c>
-      <c r="J19" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="K19" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="L19" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="M19" s="20" t="s">
-        <v>187</v>
       </c>
       <c r="N19" s="20" t="s">
         <v>4</v>
@@ -4838,33 +4715,33 @@
         <v>130</v>
       </c>
       <c r="U19" s="20" t="s">
-        <v>188</v>
+        <v>253</v>
       </c>
       <c r="V19" s="20" t="s">
-        <v>189</v>
+        <v>254</v>
       </c>
       <c r="W19" s="20"/>
       <c r="X19" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y19" s="20" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="Z19" s="20" t="s">
-        <v>191</v>
+        <v>255</v>
       </c>
       <c r="AA19" s="20" t="s">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="AB19" s="20"/>
       <c r="AC19" s="22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD19" s="22">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="AE19" s="22">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="AF19" s="22">
         <v>0</v>
@@ -4881,25 +4758,23 @@
       </c>
       <c r="AK19" s="20"/>
       <c r="AL19" s="22">
-        <v>63.28</v>
-      </c>
-      <c r="AM19" s="22">
-        <v>5.7</v>
-      </c>
+        <v>34.98</v>
+      </c>
+      <c r="AM19" s="22"/>
       <c r="AN19" s="22">
-        <v>68.98</v>
+        <v>34.98</v>
       </c>
       <c r="AO19" s="22">
-        <v>10.82</v>
+        <v>5.73</v>
       </c>
       <c r="AP19" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ19" s="22">
-        <v>16.48</v>
+        <v>8.67</v>
       </c>
       <c r="AR19" s="22">
-        <v>98.88</v>
+        <v>51.98</v>
       </c>
       <c r="AS19" s="22"/>
       <c r="AT19" s="22">
@@ -4929,9 +4804,7 @@
       <c r="BP19" s="22"/>
       <c r="BQ19" s="22"/>
       <c r="BR19" s="22"/>
-      <c r="BS19" s="22">
-        <v>5.7</v>
-      </c>
+      <c r="BS19" s="22"/>
       <c r="BT19" s="22"/>
       <c r="BU19" s="22"/>
       <c r="BV19" s="22"/>
@@ -4953,15 +4826,14 @@
       <c r="CL19" s="22"/>
       <c r="CM19" s="22"/>
       <c r="CN19" s="23"/>
-      <c r="CO19" s="23"/>
+      <c r="CO19" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP19" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ19" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR19" s="22">
-        <v>120</v>
+        <v>136</v>
+      </c>
+      <c r="CQ19" s="22">
+        <v>46</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -4969,10 +4841,10 @@
         <v>15</v>
       </c>
       <c r="B20" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>6</v>
@@ -4981,22 +4853,24 @@
         <v>4</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H20" s="20"/>
       <c r="I20" s="20" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="J20" s="20" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K20" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="L20" s="20"/>
+        <v>123</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>260</v>
+      </c>
       <c r="M20" s="20"/>
       <c r="N20" s="20" t="s">
         <v>4</v>
@@ -5018,33 +4892,37 @@
         <v>130</v>
       </c>
       <c r="U20" s="20" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="V20" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="W20" s="20"/>
+        <v>262</v>
+      </c>
+      <c r="W20" s="20" t="s">
+        <v>263</v>
+      </c>
       <c r="X20" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y20" s="20" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Z20" s="20" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AA20" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="AB20" s="20"/>
+        <v>266</v>
+      </c>
+      <c r="AB20" s="20" t="s">
+        <v>267</v>
+      </c>
       <c r="AC20" s="22">
         <v>1</v>
       </c>
       <c r="AD20" s="22">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="AE20" s="22">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="AF20" s="22">
         <v>0</v>
@@ -5061,25 +4939,23 @@
       </c>
       <c r="AK20" s="20"/>
       <c r="AL20" s="22">
-        <v>230.36</v>
-      </c>
-      <c r="AM20" s="22">
-        <v>144.9</v>
-      </c>
+        <v>16.87</v>
+      </c>
+      <c r="AM20" s="22"/>
       <c r="AN20" s="22">
-        <v>375.26</v>
+        <v>16.87</v>
       </c>
       <c r="AO20" s="22">
-        <v>39.39</v>
+        <v>2.76</v>
       </c>
       <c r="AP20" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ20" s="22">
-        <v>83.45</v>
+        <v>4.44</v>
       </c>
       <c r="AR20" s="22">
-        <v>500.7</v>
+        <v>26.67</v>
       </c>
       <c r="AS20" s="22"/>
       <c r="AT20" s="22">
@@ -5089,18 +4965,14 @@
       <c r="AV20" s="22"/>
       <c r="AW20" s="20"/>
       <c r="AX20" s="22"/>
-      <c r="AY20" s="22">
-        <v>135</v>
-      </c>
+      <c r="AY20" s="22"/>
       <c r="AZ20" s="22"/>
       <c r="BA20" s="22"/>
       <c r="BB20" s="22"/>
       <c r="BC20" s="22"/>
       <c r="BD20" s="22"/>
       <c r="BE20" s="22"/>
-      <c r="BF20" s="22">
-        <v>9.9</v>
-      </c>
+      <c r="BF20" s="22"/>
       <c r="BG20" s="22"/>
       <c r="BH20" s="22"/>
       <c r="BI20" s="22"/>
@@ -5135,26 +5007,23 @@
       <c r="CL20" s="22"/>
       <c r="CM20" s="22"/>
       <c r="CN20" s="22"/>
-      <c r="CO20" s="22"/>
+      <c r="CO20" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP20" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ20" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR20" s="22">
-        <v>110</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="CQ20" s="22"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="18.1322" customHeight="1">
       <c r="A21" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B21" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>6</v>
@@ -5163,21 +5032,27 @@
         <v>4</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G21" s="20"/>
+        <v>120</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>268</v>
+      </c>
       <c r="H21" s="20"/>
       <c r="I21" s="20" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="K21" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
+        <v>151</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="M21" s="20" t="s">
+        <v>271</v>
+      </c>
       <c r="N21" s="20" t="s">
         <v>4</v>
       </c>
@@ -5198,33 +5073,35 @@
         <v>130</v>
       </c>
       <c r="U21" s="20" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="V21" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="W21" s="20"/>
+        <v>273</v>
+      </c>
+      <c r="W21" s="20" t="s">
+        <v>274</v>
+      </c>
       <c r="X21" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y21" s="20" t="s">
-        <v>160</v>
+        <v>275</v>
       </c>
       <c r="Z21" s="20" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="AA21" s="20" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="AB21" s="20"/>
       <c r="AC21" s="22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD21" s="22">
-        <v>850</v>
+        <v>43</v>
       </c>
       <c r="AE21" s="22">
-        <v>850</v>
+        <v>43</v>
       </c>
       <c r="AF21" s="22">
         <v>0</v>
@@ -5234,30 +5111,30 @@
       </c>
       <c r="AH21" s="22"/>
       <c r="AI21" s="22">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AJ21" s="22">
         <v>0</v>
       </c>
       <c r="AK21" s="20"/>
       <c r="AL21" s="22">
-        <v>223.13</v>
+        <v>39.8</v>
       </c>
       <c r="AM21" s="22"/>
       <c r="AN21" s="22">
-        <v>223.13</v>
+        <v>39.8</v>
       </c>
       <c r="AO21" s="22">
-        <v>15.62</v>
+        <v>6.52</v>
       </c>
       <c r="AP21" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ21" s="22">
-        <v>48.27</v>
+        <v>9.78</v>
       </c>
       <c r="AR21" s="22">
-        <v>289.62</v>
+        <v>58.7</v>
       </c>
       <c r="AS21" s="22"/>
       <c r="AT21" s="22">
@@ -5309,24 +5186,25 @@
       <c r="CL21" s="22"/>
       <c r="CM21" s="22"/>
       <c r="CN21" s="23"/>
-      <c r="CO21" s="23"/>
+      <c r="CO21" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP21" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ21" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR21" s="22"/>
+        <v>136</v>
+      </c>
+      <c r="CQ21" s="22">
+        <v>43</v>
+      </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="18.1322" customHeight="1">
       <c r="A22" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B22" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D22" s="20" t="s">
         <v>6</v>
@@ -5335,28 +5213,26 @@
         <v>4</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="H22" s="20" t="s">
-        <v>269</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="H22" s="20"/>
       <c r="I22" s="20" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="J22" s="20" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="K22" s="20" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="L22" s="20" t="s">
-        <v>145</v>
+        <v>230</v>
       </c>
       <c r="M22" s="20" t="s">
-        <v>146</v>
+        <v>231</v>
       </c>
       <c r="N22" s="20" t="s">
         <v>4</v>
@@ -5378,35 +5254,35 @@
         <v>130</v>
       </c>
       <c r="U22" s="20" t="s">
-        <v>147</v>
+        <v>232</v>
       </c>
       <c r="V22" s="20" t="s">
-        <v>148</v>
+        <v>233</v>
       </c>
       <c r="W22" s="20" t="s">
-        <v>149</v>
+        <v>234</v>
       </c>
       <c r="X22" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y22" s="20" t="s">
-        <v>150</v>
+        <v>235</v>
       </c>
       <c r="Z22" s="20" t="s">
-        <v>151</v>
+        <v>236</v>
       </c>
       <c r="AA22" s="20" t="s">
-        <v>152</v>
+        <v>237</v>
       </c>
       <c r="AB22" s="20"/>
       <c r="AC22" s="22">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AD22" s="22">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AE22" s="22">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AF22" s="22">
         <v>0</v>
@@ -5423,25 +5299,23 @@
       </c>
       <c r="AK22" s="20"/>
       <c r="AL22" s="22">
-        <v>54.91</v>
-      </c>
-      <c r="AM22" s="22">
-        <v>25.6</v>
-      </c>
+        <v>38.55</v>
+      </c>
+      <c r="AM22" s="22"/>
       <c r="AN22" s="22">
-        <v>80.51</v>
+        <v>38.55</v>
       </c>
       <c r="AO22" s="22">
-        <v>9.39</v>
+        <v>6.32</v>
       </c>
       <c r="AP22" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ22" s="22">
-        <v>18.5</v>
+        <v>9.49</v>
       </c>
       <c r="AR22" s="22">
-        <v>111</v>
+        <v>56.96</v>
       </c>
       <c r="AS22" s="22"/>
       <c r="AT22" s="22">
@@ -5459,9 +5333,7 @@
       <c r="BD22" s="22"/>
       <c r="BE22" s="22"/>
       <c r="BF22" s="22"/>
-      <c r="BG22" s="22">
-        <v>19.9</v>
-      </c>
+      <c r="BG22" s="22"/>
       <c r="BH22" s="22"/>
       <c r="BI22" s="22"/>
       <c r="BJ22" s="22"/>
@@ -5473,9 +5345,7 @@
       <c r="BP22" s="22"/>
       <c r="BQ22" s="22"/>
       <c r="BR22" s="22"/>
-      <c r="BS22" s="22">
-        <v>5.7</v>
-      </c>
+      <c r="BS22" s="22"/>
       <c r="BT22" s="22"/>
       <c r="BU22" s="22"/>
       <c r="BV22" s="22"/>
@@ -5497,15 +5367,14 @@
       <c r="CL22" s="22"/>
       <c r="CM22" s="22"/>
       <c r="CN22" s="22"/>
-      <c r="CO22" s="22"/>
+      <c r="CO22" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP22" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ22" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR22" s="22">
-        <v>80</v>
+        <v>136</v>
+      </c>
+      <c r="CQ22" s="22">
+        <v>50</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -5513,10 +5382,10 @@
         <v>15</v>
       </c>
       <c r="B23" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>6</v>
@@ -5525,27 +5394,23 @@
         <v>4</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="H23" s="20"/>
       <c r="I23" s="20" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="J23" s="20" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="K23" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="L23" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="M23" s="20" t="s">
-        <v>197</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
       <c r="N23" s="20" t="s">
         <v>4</v>
       </c>
@@ -5566,37 +5431,33 @@
         <v>130</v>
       </c>
       <c r="U23" s="20" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="V23" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="W23" s="20" t="s">
-        <v>200</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="W23" s="20"/>
       <c r="X23" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y23" s="20" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="Z23" s="20" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="AA23" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB23" s="20" t="s">
-        <v>136</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="AB23" s="20"/>
       <c r="AC23" s="22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD23" s="22">
-        <v>24.7</v>
+        <v>43</v>
       </c>
       <c r="AE23" s="22">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="AF23" s="22">
         <v>0</v>
@@ -5613,23 +5474,23 @@
       </c>
       <c r="AK23" s="20"/>
       <c r="AL23" s="22">
-        <v>32.25</v>
+        <v>39.8</v>
       </c>
       <c r="AM23" s="22"/>
       <c r="AN23" s="22">
-        <v>32.25</v>
+        <v>39.8</v>
       </c>
       <c r="AO23" s="22">
-        <v>5.51</v>
+        <v>6.52</v>
       </c>
       <c r="AP23" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ23" s="22">
-        <v>8.07</v>
+        <v>9.78</v>
       </c>
       <c r="AR23" s="22">
-        <v>48.43</v>
+        <v>58.7</v>
       </c>
       <c r="AS23" s="22"/>
       <c r="AT23" s="22">
@@ -5681,15 +5542,14 @@
       <c r="CL23" s="22"/>
       <c r="CM23" s="22"/>
       <c r="CN23" s="23"/>
-      <c r="CO23" s="23"/>
+      <c r="CO23" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP23" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ23" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR23" s="22">
-        <v>26</v>
+        <v>136</v>
+      </c>
+      <c r="CQ23" s="22">
+        <v>43</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -5697,10 +5557,10 @@
         <v>15</v>
       </c>
       <c r="B24" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D24" s="20" t="s">
         <v>6</v>
@@ -5709,28 +5569,26 @@
         <v>4</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="H24" s="20" t="s">
-        <v>275</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="H24" s="20"/>
       <c r="I24" s="20" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="J24" s="20" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="K24" s="20" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="L24" s="20" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="M24" s="20" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="N24" s="20" t="s">
         <v>4</v>
@@ -5752,35 +5610,37 @@
         <v>130</v>
       </c>
       <c r="U24" s="20" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="V24" s="20" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="W24" s="20" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="X24" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y24" s="20" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="Z24" s="20" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="AA24" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="AB24" s="20"/>
+        <v>293</v>
+      </c>
+      <c r="AB24" s="20" t="s">
+        <v>267</v>
+      </c>
       <c r="AC24" s="22">
         <v>1</v>
       </c>
       <c r="AD24" s="22">
-        <v>150</v>
+        <v>165.5</v>
       </c>
       <c r="AE24" s="22">
-        <v>150</v>
+        <v>165.5</v>
       </c>
       <c r="AF24" s="22">
         <v>0</v>
@@ -5797,25 +5657,25 @@
       </c>
       <c r="AK24" s="20"/>
       <c r="AL24" s="22">
-        <v>73.92</v>
+        <v>83.78</v>
       </c>
       <c r="AM24" s="22">
-        <v>13.6</v>
+        <v>5.7</v>
       </c>
       <c r="AN24" s="22">
-        <v>87.52</v>
+        <v>89.48</v>
       </c>
       <c r="AO24" s="22">
-        <v>12.64</v>
+        <v>13.73</v>
       </c>
       <c r="AP24" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ24" s="22">
-        <v>20.55</v>
+        <v>21.17</v>
       </c>
       <c r="AR24" s="22">
-        <v>123.31</v>
+        <v>126.98</v>
       </c>
       <c r="AS24" s="22"/>
       <c r="AT24" s="22">
@@ -5832,9 +5692,7 @@
       <c r="BC24" s="22"/>
       <c r="BD24" s="22"/>
       <c r="BE24" s="22"/>
-      <c r="BF24" s="22">
-        <v>9.9</v>
-      </c>
+      <c r="BF24" s="22"/>
       <c r="BG24" s="22"/>
       <c r="BH24" s="22"/>
       <c r="BI24" s="22"/>
@@ -5847,14 +5705,14 @@
       <c r="BP24" s="22"/>
       <c r="BQ24" s="22"/>
       <c r="BR24" s="22"/>
-      <c r="BS24" s="22"/>
+      <c r="BS24" s="22">
+        <v>5.7</v>
+      </c>
       <c r="BT24" s="22"/>
       <c r="BU24" s="22"/>
       <c r="BV24" s="22"/>
       <c r="BW24" s="22"/>
-      <c r="BX24" s="22">
-        <v>3.7</v>
-      </c>
+      <c r="BX24" s="22"/>
       <c r="BY24" s="22"/>
       <c r="BZ24" s="22"/>
       <c r="CA24" s="22"/>
@@ -5871,15 +5729,14 @@
       <c r="CL24" s="22"/>
       <c r="CM24" s="22"/>
       <c r="CN24" s="22"/>
-      <c r="CO24" s="22"/>
+      <c r="CO24" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP24" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ24" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR24" s="22">
-        <v>150</v>
+        <v>136</v>
+      </c>
+      <c r="CQ24" s="22">
+        <v>170</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -5887,10 +5744,10 @@
         <v>15</v>
       </c>
       <c r="B25" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>6</v>
@@ -5899,20 +5756,20 @@
         <v>4</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="H25" s="20"/>
       <c r="I25" s="20" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="K25" s="20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="L25" s="20"/>
       <c r="M25" s="20"/>
@@ -5936,35 +5793,37 @@
         <v>130</v>
       </c>
       <c r="U25" s="20" t="s">
-        <v>257</v>
+        <v>297</v>
       </c>
       <c r="V25" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="W25" s="20"/>
+        <v>298</v>
+      </c>
+      <c r="W25" s="20" t="s">
+        <v>299</v>
+      </c>
       <c r="X25" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y25" s="20" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Z25" s="20" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AA25" s="20" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="AB25" s="20" t="s">
-        <v>136</v>
+        <v>267</v>
       </c>
       <c r="AC25" s="22">
         <v>1</v>
       </c>
       <c r="AD25" s="22">
-        <v>111</v>
+        <v>375000e-6</v>
       </c>
       <c r="AE25" s="22">
-        <v>111</v>
+        <v>375000e-6</v>
       </c>
       <c r="AF25" s="22">
         <v>0</v>
@@ -5981,25 +5840,25 @@
       </c>
       <c r="AK25" s="20"/>
       <c r="AL25" s="22">
-        <v>59.14</v>
+        <v>33.73</v>
       </c>
       <c r="AM25" s="22">
-        <v>13.6</v>
+        <v>5.7</v>
       </c>
       <c r="AN25" s="22">
-        <v>72.74</v>
+        <v>39.43</v>
       </c>
       <c r="AO25" s="22">
-        <v>10.11</v>
+        <v>5.53</v>
       </c>
       <c r="AP25" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ25" s="22">
-        <v>17.09</v>
+        <v>9.52</v>
       </c>
       <c r="AR25" s="22">
-        <v>102.54</v>
+        <v>57.08</v>
       </c>
       <c r="AS25" s="22"/>
       <c r="AT25" s="22">
@@ -6016,9 +5875,7 @@
       <c r="BC25" s="22"/>
       <c r="BD25" s="22"/>
       <c r="BE25" s="22"/>
-      <c r="BF25" s="22">
-        <v>9.9</v>
-      </c>
+      <c r="BF25" s="22"/>
       <c r="BG25" s="22"/>
       <c r="BH25" s="22"/>
       <c r="BI25" s="22"/>
@@ -6031,14 +5888,14 @@
       <c r="BP25" s="22"/>
       <c r="BQ25" s="22"/>
       <c r="BR25" s="22"/>
-      <c r="BS25" s="22"/>
+      <c r="BS25" s="22">
+        <v>5.7</v>
+      </c>
       <c r="BT25" s="22"/>
       <c r="BU25" s="22"/>
       <c r="BV25" s="22"/>
       <c r="BW25" s="22"/>
-      <c r="BX25" s="22">
-        <v>3.7</v>
-      </c>
+      <c r="BX25" s="22"/>
       <c r="BY25" s="22"/>
       <c r="BZ25" s="22"/>
       <c r="CA25" s="22"/>
@@ -6055,15 +5912,14 @@
       <c r="CL25" s="22"/>
       <c r="CM25" s="22"/>
       <c r="CN25" s="23"/>
-      <c r="CO25" s="23"/>
+      <c r="CO25" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP25" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ25" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR25" s="22">
-        <v>120</v>
+        <v>136</v>
+      </c>
+      <c r="CQ25" s="22">
+        <v>1</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -6071,10 +5927,10 @@
         <v>15</v>
       </c>
       <c r="B26" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D26" s="20" t="s">
         <v>6</v>
@@ -6083,22 +5939,24 @@
         <v>4</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="H26" s="20"/>
       <c r="I26" s="20" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="J26" s="20" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="K26" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="L26" s="20"/>
+        <v>123</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>162</v>
+      </c>
       <c r="M26" s="20"/>
       <c r="N26" s="20" t="s">
         <v>4</v>
@@ -6120,35 +5978,37 @@
         <v>130</v>
       </c>
       <c r="U26" s="20" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="V26" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="W26" s="20"/>
+        <v>164</v>
+      </c>
+      <c r="W26" s="20" t="s">
+        <v>165</v>
+      </c>
       <c r="X26" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y26" s="20" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="Z26" s="20" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="AA26" s="20" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="AB26" s="20" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="AC26" s="22">
         <v>1</v>
       </c>
       <c r="AD26" s="22">
-        <v>40</v>
+        <v>168.5</v>
       </c>
       <c r="AE26" s="22">
-        <v>40</v>
+        <v>168.5</v>
       </c>
       <c r="AF26" s="22">
         <v>0</v>
@@ -6165,25 +6025,25 @@
       </c>
       <c r="AK26" s="20"/>
       <c r="AL26" s="22">
-        <v>39.8</v>
+        <v>412.2</v>
       </c>
       <c r="AM26" s="22">
-        <v>5.7</v>
+        <v>205</v>
       </c>
       <c r="AN26" s="22">
-        <v>45.5</v>
+        <v>617.2</v>
       </c>
       <c r="AO26" s="22">
-        <v>6.81</v>
+        <v>67.56</v>
       </c>
       <c r="AP26" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ26" s="22">
-        <v>10.98</v>
+        <v>137.47</v>
       </c>
       <c r="AR26" s="22">
-        <v>65.89</v>
+        <v>824.83</v>
       </c>
       <c r="AS26" s="22"/>
       <c r="AT26" s="22">
@@ -6193,7 +6053,9 @@
       <c r="AV26" s="22"/>
       <c r="AW26" s="20"/>
       <c r="AX26" s="22"/>
-      <c r="AY26" s="22"/>
+      <c r="AY26" s="22">
+        <v>205</v>
+      </c>
       <c r="AZ26" s="22"/>
       <c r="BA26" s="22"/>
       <c r="BB26" s="22"/>
@@ -6213,9 +6075,7 @@
       <c r="BP26" s="22"/>
       <c r="BQ26" s="22"/>
       <c r="BR26" s="22"/>
-      <c r="BS26" s="22">
-        <v>5.7</v>
-      </c>
+      <c r="BS26" s="22"/>
       <c r="BT26" s="22"/>
       <c r="BU26" s="22"/>
       <c r="BV26" s="22"/>
@@ -6237,15 +6097,14 @@
       <c r="CL26" s="22"/>
       <c r="CM26" s="22"/>
       <c r="CN26" s="22"/>
-      <c r="CO26" s="22"/>
+      <c r="CO26" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP26" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ26" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR26" s="22">
-        <v>40</v>
+        <v>136</v>
+      </c>
+      <c r="CQ26" s="22">
+        <v>170</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -6253,10 +6112,10 @@
         <v>15</v>
       </c>
       <c r="B27" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D27" s="20" t="s">
         <v>6</v>
@@ -6265,26 +6124,26 @@
         <v>4</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="H27" s="20"/>
       <c r="I27" s="20" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="K27" s="20" t="s">
-        <v>294</v>
+        <v>123</v>
       </c>
       <c r="L27" s="20" t="s">
-        <v>295</v>
+        <v>140</v>
       </c>
       <c r="M27" s="20" t="s">
-        <v>296</v>
+        <v>141</v>
       </c>
       <c r="N27" s="20" t="s">
         <v>4</v>
@@ -6306,43 +6165,43 @@
         <v>130</v>
       </c>
       <c r="U27" s="20" t="s">
-        <v>297</v>
+        <v>142</v>
       </c>
       <c r="V27" s="20" t="s">
-        <v>298</v>
+        <v>143</v>
       </c>
       <c r="W27" s="20"/>
       <c r="X27" s="20" t="s">
-        <v>299</v>
+        <v>127</v>
       </c>
       <c r="Y27" s="20" t="s">
-        <v>300</v>
+        <v>144</v>
       </c>
       <c r="Z27" s="20" t="s">
-        <v>301</v>
+        <v>145</v>
       </c>
       <c r="AA27" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="AB27" s="20"/>
+        <v>146</v>
+      </c>
+      <c r="AB27" s="20" t="s">
+        <v>147</v>
+      </c>
       <c r="AC27" s="22">
         <v>1</v>
       </c>
       <c r="AD27" s="22">
-        <v>250</v>
+        <v>99.5</v>
       </c>
       <c r="AE27" s="22">
-        <v>250</v>
+        <v>99.5</v>
       </c>
       <c r="AF27" s="22">
-        <v>1.728</v>
+        <v>0</v>
       </c>
       <c r="AG27" s="22">
-        <v>2.02</v>
-      </c>
-      <c r="AH27" s="22">
-        <v>9.8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH27" s="22"/>
       <c r="AI27" s="22">
         <v>0</v>
       </c>
@@ -6351,23 +6210,25 @@
       </c>
       <c r="AK27" s="20"/>
       <c r="AL27" s="22">
-        <v>281.06</v>
-      </c>
-      <c r="AM27" s="22"/>
+        <v>242.47</v>
+      </c>
+      <c r="AM27" s="22">
+        <v>175</v>
+      </c>
       <c r="AN27" s="22">
-        <v>281.06</v>
+        <v>417.47</v>
       </c>
       <c r="AO27" s="22">
-        <v>48.06</v>
+        <v>39.74</v>
       </c>
       <c r="AP27" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ27" s="22">
-        <v>68.3</v>
+        <v>91.96</v>
       </c>
       <c r="AR27" s="22">
-        <v>409.82</v>
+        <v>551.77</v>
       </c>
       <c r="AS27" s="22"/>
       <c r="AT27" s="22">
@@ -6375,11 +6236,11 @@
       </c>
       <c r="AU27" s="22"/>
       <c r="AV27" s="22"/>
-      <c r="AW27" s="20" t="s">
-        <v>303</v>
-      </c>
+      <c r="AW27" s="20"/>
       <c r="AX27" s="22"/>
-      <c r="AY27" s="22"/>
+      <c r="AY27" s="22">
+        <v>175</v>
+      </c>
       <c r="AZ27" s="22"/>
       <c r="BA27" s="22"/>
       <c r="BB27" s="22"/>
@@ -6421,15 +6282,14 @@
       <c r="CL27" s="22"/>
       <c r="CM27" s="22"/>
       <c r="CN27" s="23"/>
-      <c r="CO27" s="23"/>
+      <c r="CO27" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP27" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ27" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR27" s="22">
-        <v>510</v>
+        <v>136</v>
+      </c>
+      <c r="CQ27" s="22">
+        <v>100</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -6437,10 +6297,10 @@
         <v>15</v>
       </c>
       <c r="B28" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D28" s="20" t="s">
         <v>6</v>
@@ -6449,26 +6309,32 @@
         <v>4</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G28" s="20"/>
+        <v>120</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>305</v>
+      </c>
       <c r="H28" s="20"/>
       <c r="I28" s="20" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J28" s="20" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K28" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
+        <v>123</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="M28" s="20" t="s">
+        <v>172</v>
+      </c>
       <c r="N28" s="20" t="s">
-        <v>306</v>
+        <v>4</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>307</v>
+        <v>126</v>
       </c>
       <c r="P28" s="20"/>
       <c r="Q28" s="20" t="s">
@@ -6478,14 +6344,16 @@
         <v>128</v>
       </c>
       <c r="S28" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="T28" s="20"/>
+        <v>129</v>
+      </c>
+      <c r="T28" s="20" t="s">
+        <v>130</v>
+      </c>
       <c r="U28" s="20" t="s">
-        <v>4</v>
+        <v>173</v>
       </c>
       <c r="V28" s="20" t="s">
-        <v>126</v>
+        <v>174</v>
       </c>
       <c r="W28" s="20"/>
       <c r="X28" s="20" t="s">
@@ -6495,20 +6363,22 @@
         <v>128</v>
       </c>
       <c r="Z28" s="20" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="AA28" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB28" s="20"/>
+        <v>176</v>
+      </c>
+      <c r="AB28" s="20" t="s">
+        <v>267</v>
+      </c>
       <c r="AC28" s="22">
         <v>1</v>
       </c>
       <c r="AD28" s="22">
-        <v>10000</v>
+        <v>62</v>
       </c>
       <c r="AE28" s="22">
-        <v>10000</v>
+        <v>62</v>
       </c>
       <c r="AF28" s="22">
         <v>0</v>
@@ -6518,30 +6388,32 @@
       </c>
       <c r="AH28" s="22"/>
       <c r="AI28" s="22">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="AJ28" s="22">
         <v>0</v>
       </c>
       <c r="AK28" s="20"/>
       <c r="AL28" s="22">
-        <v>241.36</v>
-      </c>
-      <c r="AM28" s="22"/>
+        <v>45.59</v>
+      </c>
+      <c r="AM28" s="22">
+        <v>91.32</v>
+      </c>
       <c r="AN28" s="22">
-        <v>241.36</v>
+        <v>136.91</v>
       </c>
       <c r="AO28" s="22">
-        <v>16.9</v>
+        <v>7.47</v>
       </c>
       <c r="AP28" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ28" s="22">
-        <v>52.17</v>
+        <v>29.39</v>
       </c>
       <c r="AR28" s="22">
-        <v>313.03</v>
+        <v>176.37</v>
       </c>
       <c r="AS28" s="22"/>
       <c r="AT28" s="22">
@@ -6551,7 +6423,9 @@
       <c r="AV28" s="22"/>
       <c r="AW28" s="20"/>
       <c r="AX28" s="22"/>
-      <c r="AY28" s="22"/>
+      <c r="AY28" s="22">
+        <v>91.32</v>
+      </c>
       <c r="AZ28" s="22"/>
       <c r="BA28" s="22"/>
       <c r="BB28" s="22"/>
@@ -6593,24 +6467,25 @@
       <c r="CL28" s="22"/>
       <c r="CM28" s="22"/>
       <c r="CN28" s="22"/>
-      <c r="CO28" s="22"/>
+      <c r="CO28" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP28" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ28" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR28" s="22"/>
+        <v>136</v>
+      </c>
+      <c r="CQ28" s="22">
+        <v>62</v>
+      </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="18.1322" customHeight="1">
       <c r="A29" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B29" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D29" s="20" t="s">
         <v>6</v>
@@ -6619,27 +6494,23 @@
         <v>4</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H29" s="20"/>
       <c r="I29" s="20" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="K29" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="L29" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="M29" s="20" t="s">
-        <v>279</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
       <c r="N29" s="20" t="s">
         <v>4</v>
       </c>
@@ -6660,37 +6531,35 @@
         <v>130</v>
       </c>
       <c r="U29" s="20" t="s">
-        <v>280</v>
+        <v>152</v>
       </c>
       <c r="V29" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="W29" s="20" t="s">
-        <v>282</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="W29" s="20"/>
       <c r="X29" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y29" s="20" t="s">
-        <v>283</v>
+        <v>154</v>
       </c>
       <c r="Z29" s="20" t="s">
-        <v>284</v>
+        <v>155</v>
       </c>
       <c r="AA29" s="20" t="s">
-        <v>285</v>
+        <v>156</v>
       </c>
       <c r="AB29" s="20" t="s">
-        <v>290</v>
+        <v>147</v>
       </c>
       <c r="AC29" s="22">
         <v>1</v>
       </c>
       <c r="AD29" s="22">
-        <v>91.5</v>
+        <v>40</v>
       </c>
       <c r="AE29" s="22">
-        <v>91.5</v>
+        <v>40</v>
       </c>
       <c r="AF29" s="22">
         <v>0</v>
@@ -6707,25 +6576,23 @@
       </c>
       <c r="AK29" s="20"/>
       <c r="AL29" s="22">
-        <v>49.28</v>
-      </c>
-      <c r="AM29" s="22">
-        <v>9.9</v>
-      </c>
+        <v>39.8</v>
+      </c>
+      <c r="AM29" s="22"/>
       <c r="AN29" s="22">
-        <v>59.18</v>
+        <v>39.8</v>
       </c>
       <c r="AO29" s="22">
-        <v>8.43</v>
+        <v>6.52</v>
       </c>
       <c r="AP29" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ29" s="22">
-        <v>14.05</v>
+        <v>9.78</v>
       </c>
       <c r="AR29" s="22">
-        <v>84.26</v>
+        <v>58.7</v>
       </c>
       <c r="AS29" s="22"/>
       <c r="AT29" s="22">
@@ -6742,9 +6609,7 @@
       <c r="BC29" s="22"/>
       <c r="BD29" s="22"/>
       <c r="BE29" s="22"/>
-      <c r="BF29" s="22">
-        <v>9.9</v>
-      </c>
+      <c r="BF29" s="22"/>
       <c r="BG29" s="22"/>
       <c r="BH29" s="22"/>
       <c r="BI29" s="22"/>
@@ -6779,15 +6644,14 @@
       <c r="CL29" s="22"/>
       <c r="CM29" s="22"/>
       <c r="CN29" s="23"/>
-      <c r="CO29" s="23"/>
+      <c r="CO29" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP29" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ29" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR29" s="22">
-        <v>92</v>
+        <v>136</v>
+      </c>
+      <c r="CQ29" s="22">
+        <v>40</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -6795,10 +6659,10 @@
         <v>15</v>
       </c>
       <c r="B30" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D30" s="20" t="s">
         <v>6</v>
@@ -6807,25 +6671,25 @@
         <v>4</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G30" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="J30" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="H30" s="20" t="s">
+      <c r="K30" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="L30" s="20" t="s">
         <v>312</v>
       </c>
-      <c r="I30" s="20" t="s">
+      <c r="M30" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="J30" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="K30" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="L30" s="20"/>
-      <c r="M30" s="20"/>
       <c r="N30" s="20" t="s">
         <v>4</v>
       </c>
@@ -6846,14 +6710,16 @@
         <v>130</v>
       </c>
       <c r="U30" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="V30" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="V30" s="20" t="s">
+      <c r="W30" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="W30" s="20"/>
       <c r="X30" s="20" t="s">
-        <v>243</v>
+        <v>127</v>
       </c>
       <c r="Y30" s="20" t="s">
         <v>317</v>
@@ -6866,48 +6732,46 @@
       </c>
       <c r="AB30" s="20"/>
       <c r="AC30" s="22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD30" s="22">
-        <v>9</v>
+        <v>458</v>
       </c>
       <c r="AE30" s="22">
-        <v>9</v>
+        <v>458</v>
       </c>
       <c r="AF30" s="22">
-        <v>288000e-6</v>
+        <v>0</v>
       </c>
       <c r="AG30" s="22">
-        <v>288000e-6</v>
+        <v>0</v>
       </c>
       <c r="AH30" s="22"/>
       <c r="AI30" s="22">
-        <v>0</v>
+        <v>800000e-6</v>
       </c>
       <c r="AJ30" s="22">
         <v>0</v>
       </c>
       <c r="AK30" s="20"/>
       <c r="AL30" s="22">
-        <v>67.31</v>
-      </c>
-      <c r="AM30" s="22">
-        <v>5.57</v>
-      </c>
+        <v>185.89</v>
+      </c>
+      <c r="AM30" s="22"/>
       <c r="AN30" s="22">
-        <v>72.88</v>
+        <v>185.89</v>
       </c>
       <c r="AO30" s="22">
-        <v>11.51</v>
+        <v>30.51</v>
       </c>
       <c r="AP30" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ30" s="22">
-        <v>17.39</v>
+        <v>43.8</v>
       </c>
       <c r="AR30" s="22">
-        <v>104.38</v>
+        <v>262.8</v>
       </c>
       <c r="AS30" s="22"/>
       <c r="AT30" s="22">
@@ -6915,9 +6779,7 @@
       </c>
       <c r="AU30" s="22"/>
       <c r="AV30" s="22"/>
-      <c r="AW30" s="20" t="s">
-        <v>303</v>
-      </c>
+      <c r="AW30" s="20"/>
       <c r="AX30" s="22"/>
       <c r="AY30" s="22"/>
       <c r="AZ30" s="22"/>
@@ -6938,17 +6800,13 @@
       <c r="BO30" s="22"/>
       <c r="BP30" s="22"/>
       <c r="BQ30" s="22"/>
-      <c r="BR30" s="22">
-        <v>1.87</v>
-      </c>
+      <c r="BR30" s="22"/>
       <c r="BS30" s="22"/>
       <c r="BT30" s="22"/>
       <c r="BU30" s="22"/>
       <c r="BV30" s="22"/>
       <c r="BW30" s="22"/>
-      <c r="BX30" s="22">
-        <v>3.7</v>
-      </c>
+      <c r="BX30" s="22"/>
       <c r="BY30" s="22"/>
       <c r="BZ30" s="22"/>
       <c r="CA30" s="22"/>
@@ -6965,26 +6823,23 @@
       <c r="CL30" s="22"/>
       <c r="CM30" s="22"/>
       <c r="CN30" s="22"/>
-      <c r="CO30" s="22"/>
+      <c r="CO30" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP30" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ30" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR30" s="22">
-        <v>72</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="CQ30" s="22"/>
     </row>
     <row r="31" s="1" customFormat="1" ht="18.1322" customHeight="1">
       <c r="A31" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B31" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D31" s="20" t="s">
         <v>6</v>
@@ -6993,7 +6848,7 @@
         <v>4</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G31" s="20" t="s">
         <v>320</v>
@@ -7003,17 +6858,13 @@
         <v>321</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="K31" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="L31" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="M31" s="20" t="s">
         <v>323</v>
       </c>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
       <c r="N31" s="20" t="s">
         <v>4</v>
       </c>
@@ -7041,34 +6892,34 @@
       </c>
       <c r="W31" s="20"/>
       <c r="X31" s="20" t="s">
-        <v>127</v>
+        <v>326</v>
       </c>
       <c r="Y31" s="20" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z31" s="20" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AA31" s="20" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AB31" s="20" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="AC31" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD31" s="22">
-        <v>78.5</v>
+        <v>320</v>
       </c>
       <c r="AE31" s="22">
-        <v>78.5</v>
+        <v>320</v>
       </c>
       <c r="AF31" s="22">
-        <v>0</v>
+        <v>2.937</v>
       </c>
       <c r="AG31" s="22">
-        <v>0</v>
+        <v>2.937</v>
       </c>
       <c r="AH31" s="22"/>
       <c r="AI31" s="22">
@@ -7079,23 +6930,25 @@
       </c>
       <c r="AK31" s="20"/>
       <c r="AL31" s="22">
-        <v>173.92</v>
-      </c>
-      <c r="AM31" s="22"/>
+        <v>473.01</v>
+      </c>
+      <c r="AM31" s="22">
+        <v>32.54</v>
+      </c>
       <c r="AN31" s="22">
-        <v>173.92</v>
+        <v>505.55</v>
       </c>
       <c r="AO31" s="22">
-        <v>29.74</v>
+        <v>77.53</v>
       </c>
       <c r="AP31" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ31" s="22">
-        <v>41.25</v>
+        <v>117.14</v>
       </c>
       <c r="AR31" s="22">
-        <v>247.51</v>
+        <v>702.82</v>
       </c>
       <c r="AS31" s="22"/>
       <c r="AT31" s="22">
@@ -7103,7 +6956,9 @@
       </c>
       <c r="AU31" s="22"/>
       <c r="AV31" s="22"/>
-      <c r="AW31" s="20"/>
+      <c r="AW31" s="20" t="s">
+        <v>330</v>
+      </c>
       <c r="AX31" s="22"/>
       <c r="AY31" s="22"/>
       <c r="AZ31" s="22"/>
@@ -7146,16 +7001,17 @@
       <c r="CK31" s="22"/>
       <c r="CL31" s="22"/>
       <c r="CM31" s="22"/>
-      <c r="CN31" s="23"/>
-      <c r="CO31" s="23"/>
+      <c r="CN31" s="23">
+        <v>32.54</v>
+      </c>
+      <c r="CO31" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP31" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ31" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR31" s="22">
-        <v>79</v>
+        <v>136</v>
+      </c>
+      <c r="CQ31" s="22">
+        <v>740</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -7163,10 +7019,10 @@
         <v>15</v>
       </c>
       <c r="B32" s="21">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D32" s="20" t="s">
         <v>6</v>
@@ -7175,76 +7031,70 @@
         <v>4</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G32" s="20" t="s">
-        <v>329</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G32" s="20"/>
       <c r="H32" s="20"/>
       <c r="I32" s="20" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J32" s="20" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="K32" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="L32" s="20" t="s">
-        <v>331</v>
-      </c>
-      <c r="M32" s="20" t="s">
-        <v>332</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
       <c r="N32" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="O32" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="P32" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q32" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="R32" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="S32" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="T32" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="U32" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="O32" s="20" t="s">
+      <c r="V32" s="20" t="s">
         <v>126</v>
-      </c>
-      <c r="P32" s="20"/>
-      <c r="Q32" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="R32" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="S32" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="T32" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="U32" s="20" t="s">
-        <v>333</v>
-      </c>
-      <c r="V32" s="20" t="s">
-        <v>334</v>
       </c>
       <c r="W32" s="20"/>
       <c r="X32" s="20" t="s">
         <v>127</v>
       </c>
       <c r="Y32" s="20" t="s">
-        <v>190</v>
+        <v>128</v>
       </c>
       <c r="Z32" s="20" t="s">
-        <v>335</v>
+        <v>129</v>
       </c>
       <c r="AA32" s="20" t="s">
-        <v>336</v>
-      </c>
-      <c r="AB32" s="20" t="s">
-        <v>290</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="AB32" s="20"/>
       <c r="AC32" s="22">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AD32" s="22">
-        <v>421.5</v>
+        <v>800</v>
       </c>
       <c r="AE32" s="22">
-        <v>421.5</v>
+        <v>800</v>
       </c>
       <c r="AF32" s="22">
         <v>0</v>
@@ -7254,30 +7104,30 @@
       </c>
       <c r="AH32" s="22"/>
       <c r="AI32" s="22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ32" s="22">
         <v>0</v>
       </c>
       <c r="AK32" s="20"/>
       <c r="AL32" s="22">
-        <v>1042.62</v>
+        <v>758.01</v>
       </c>
       <c r="AM32" s="22"/>
       <c r="AN32" s="22">
-        <v>1042.62</v>
+        <v>758.01</v>
       </c>
       <c r="AO32" s="22">
-        <v>178.29</v>
+        <v>124.39</v>
       </c>
       <c r="AP32" s="22">
         <v>2.6</v>
       </c>
       <c r="AQ32" s="22">
-        <v>244.7</v>
+        <v>177</v>
       </c>
       <c r="AR32" s="22">
-        <v>1468.21</v>
+        <v>1062</v>
       </c>
       <c r="AS32" s="22"/>
       <c r="AT32" s="22">
@@ -7285,7 +7135,9 @@
       </c>
       <c r="AU32" s="22"/>
       <c r="AV32" s="22"/>
-      <c r="AW32" s="20"/>
+      <c r="AW32" s="20" t="s">
+        <v>339</v>
+      </c>
       <c r="AX32" s="22"/>
       <c r="AY32" s="22"/>
       <c r="AZ32" s="22"/>
@@ -7329,1303 +7181,23 @@
       <c r="CL32" s="22"/>
       <c r="CM32" s="22"/>
       <c r="CN32" s="22"/>
-      <c r="CO32" s="22"/>
+      <c r="CO32" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="CP32" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ32" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR32" s="22">
-        <v>430</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="CQ32" s="22"/>
     </row>
-    <row r="33" s="1" customFormat="1" ht="18.1322" customHeight="1">
-      <c r="A33" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" s="21">
-        <v>46203</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20" t="s">
-        <v>337</v>
-      </c>
-      <c r="I33" s="20" t="s">
-        <v>338</v>
-      </c>
-      <c r="J33" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="K33" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="L33" s="20" t="s">
-        <v>339</v>
-      </c>
-      <c r="M33" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="N33" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="O33" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="R33" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="S33" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="T33" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="U33" s="20" t="s">
-        <v>341</v>
-      </c>
-      <c r="V33" s="20" t="s">
-        <v>342</v>
-      </c>
-      <c r="W33" s="20"/>
-      <c r="X33" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y33" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="Z33" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="AA33" s="20" t="s">
-        <v>343</v>
-      </c>
-      <c r="AB33" s="20"/>
-      <c r="AC33" s="22">
-        <v>1</v>
-      </c>
-      <c r="AD33" s="22">
-        <v>55</v>
-      </c>
-      <c r="AE33" s="22">
-        <v>55</v>
-      </c>
-      <c r="AF33" s="22">
-        <v>0</v>
-      </c>
-      <c r="AG33" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH33" s="22"/>
-      <c r="AI33" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ33" s="22">
-        <v>0</v>
-      </c>
-      <c r="AK33" s="20"/>
-      <c r="AL33" s="22">
-        <v>40.49</v>
-      </c>
-      <c r="AM33" s="22"/>
-      <c r="AN33" s="22">
-        <v>40.49</v>
-      </c>
-      <c r="AO33" s="22">
-        <v>6.92</v>
-      </c>
-      <c r="AP33" s="22">
-        <v>2.6</v>
-      </c>
-      <c r="AQ33" s="22">
-        <v>10</v>
-      </c>
-      <c r="AR33" s="22">
-        <v>60.01</v>
-      </c>
-      <c r="AS33" s="22"/>
-      <c r="AT33" s="22">
-        <v>0</v>
-      </c>
-      <c r="AU33" s="22"/>
-      <c r="AV33" s="22"/>
-      <c r="AW33" s="20"/>
-      <c r="AX33" s="22"/>
-      <c r="AY33" s="22"/>
-      <c r="AZ33" s="22"/>
-      <c r="BA33" s="22"/>
-      <c r="BB33" s="22"/>
-      <c r="BC33" s="22"/>
-      <c r="BD33" s="22"/>
-      <c r="BE33" s="22"/>
-      <c r="BF33" s="22"/>
-      <c r="BG33" s="22"/>
-      <c r="BH33" s="22"/>
-      <c r="BI33" s="22"/>
-      <c r="BJ33" s="22"/>
-      <c r="BK33" s="22"/>
-      <c r="BL33" s="22"/>
-      <c r="BM33" s="22"/>
-      <c r="BN33" s="22"/>
-      <c r="BO33" s="22"/>
-      <c r="BP33" s="22"/>
-      <c r="BQ33" s="22"/>
-      <c r="BR33" s="22"/>
-      <c r="BS33" s="22"/>
-      <c r="BT33" s="22"/>
-      <c r="BU33" s="22"/>
-      <c r="BV33" s="22"/>
-      <c r="BW33" s="22"/>
-      <c r="BX33" s="22"/>
-      <c r="BY33" s="22"/>
-      <c r="BZ33" s="22"/>
-      <c r="CA33" s="22"/>
-      <c r="CB33" s="22"/>
-      <c r="CC33" s="22"/>
-      <c r="CD33" s="22"/>
-      <c r="CE33" s="22"/>
-      <c r="CF33" s="22"/>
-      <c r="CG33" s="22"/>
-      <c r="CH33" s="22"/>
-      <c r="CI33" s="22"/>
-      <c r="CJ33" s="22"/>
-      <c r="CK33" s="22"/>
-      <c r="CL33" s="22"/>
-      <c r="CM33" s="22"/>
-      <c r="CN33" s="23"/>
-      <c r="CO33" s="23"/>
-      <c r="CP33" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ33" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR33" s="22">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" ht="18.1322" customHeight="1">
-      <c r="A34" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" s="21">
-        <v>46203</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="E34" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F34" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G34" s="20" t="s">
-        <v>344</v>
-      </c>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="J34" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="K34" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="L34" s="20" t="s">
-        <v>346</v>
-      </c>
-      <c r="M34" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="N34" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="O34" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="P34" s="20"/>
-      <c r="Q34" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="R34" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="S34" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="T34" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="U34" s="20" t="s">
-        <v>348</v>
-      </c>
-      <c r="V34" s="20" t="s">
-        <v>349</v>
-      </c>
-      <c r="W34" s="20"/>
-      <c r="X34" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y34" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="Z34" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="AA34" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="AB34" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="AC34" s="22">
-        <v>1</v>
-      </c>
-      <c r="AD34" s="22">
-        <v>174.5</v>
-      </c>
-      <c r="AE34" s="22">
-        <v>174.5</v>
-      </c>
-      <c r="AF34" s="22">
-        <v>0</v>
-      </c>
-      <c r="AG34" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH34" s="22"/>
-      <c r="AI34" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="22">
-        <v>0</v>
-      </c>
-      <c r="AK34" s="20"/>
-      <c r="AL34" s="22">
-        <v>436.45</v>
-      </c>
-      <c r="AM34" s="22">
-        <v>165</v>
-      </c>
-      <c r="AN34" s="22">
-        <v>601.45</v>
-      </c>
-      <c r="AO34" s="22">
-        <v>74.63</v>
-      </c>
-      <c r="AP34" s="22">
-        <v>2.6</v>
-      </c>
-      <c r="AQ34" s="22">
-        <v>135.74</v>
-      </c>
-      <c r="AR34" s="22">
-        <v>814.42</v>
-      </c>
-      <c r="AS34" s="22"/>
-      <c r="AT34" s="22">
-        <v>0</v>
-      </c>
-      <c r="AU34" s="22"/>
-      <c r="AV34" s="22"/>
-      <c r="AW34" s="20"/>
-      <c r="AX34" s="22"/>
-      <c r="AY34" s="22"/>
-      <c r="AZ34" s="22"/>
-      <c r="BA34" s="22"/>
-      <c r="BB34" s="22"/>
-      <c r="BC34" s="22"/>
-      <c r="BD34" s="22"/>
-      <c r="BE34" s="22"/>
-      <c r="BF34" s="22"/>
-      <c r="BG34" s="22"/>
-      <c r="BH34" s="22"/>
-      <c r="BI34" s="22"/>
-      <c r="BJ34" s="22"/>
-      <c r="BK34" s="22"/>
-      <c r="BL34" s="22"/>
-      <c r="BM34" s="22"/>
-      <c r="BN34" s="22"/>
-      <c r="BO34" s="22"/>
-      <c r="BP34" s="22"/>
-      <c r="BQ34" s="22"/>
-      <c r="BR34" s="22"/>
-      <c r="BS34" s="22"/>
-      <c r="BT34" s="22"/>
-      <c r="BU34" s="22"/>
-      <c r="BV34" s="22"/>
-      <c r="BW34" s="22"/>
-      <c r="BX34" s="22"/>
-      <c r="BY34" s="22"/>
-      <c r="BZ34" s="22"/>
-      <c r="CA34" s="22"/>
-      <c r="CB34" s="22"/>
-      <c r="CC34" s="22"/>
-      <c r="CD34" s="22"/>
-      <c r="CE34" s="22"/>
-      <c r="CF34" s="22"/>
-      <c r="CG34" s="22"/>
-      <c r="CH34" s="22"/>
-      <c r="CI34" s="22"/>
-      <c r="CJ34" s="22"/>
-      <c r="CK34" s="22"/>
-      <c r="CL34" s="22"/>
-      <c r="CM34" s="22"/>
-      <c r="CN34" s="22">
-        <v>165</v>
-      </c>
-      <c r="CO34" s="22"/>
-      <c r="CP34" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ34" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR34" s="22">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" ht="18.1322" customHeight="1">
-      <c r="A35" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" s="21">
-        <v>46203</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20" t="s">
-        <v>354</v>
-      </c>
-      <c r="J35" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="K35" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="O35" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="R35" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="S35" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="T35" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="U35" s="20" t="s">
-        <v>355</v>
-      </c>
-      <c r="V35" s="20" t="s">
-        <v>356</v>
-      </c>
-      <c r="W35" s="20"/>
-      <c r="X35" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y35" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="Z35" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="AA35" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB35" s="20"/>
-      <c r="AC35" s="22">
-        <v>1</v>
-      </c>
-      <c r="AD35" s="22">
-        <v>95</v>
-      </c>
-      <c r="AE35" s="22">
-        <v>95</v>
-      </c>
-      <c r="AF35" s="22">
-        <v>0</v>
-      </c>
-      <c r="AG35" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH35" s="22"/>
-      <c r="AI35" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ35" s="22">
-        <v>0</v>
-      </c>
-      <c r="AK35" s="20"/>
-      <c r="AL35" s="22">
-        <v>58.69</v>
-      </c>
-      <c r="AM35" s="22">
-        <v>5.7</v>
-      </c>
-      <c r="AN35" s="22">
-        <v>64.39</v>
-      </c>
-      <c r="AO35" s="22">
-        <v>10.04</v>
-      </c>
-      <c r="AP35" s="22">
-        <v>2.6</v>
-      </c>
-      <c r="AQ35" s="22">
-        <v>15.41</v>
-      </c>
-      <c r="AR35" s="22">
-        <v>92.44</v>
-      </c>
-      <c r="AS35" s="22"/>
-      <c r="AT35" s="22">
-        <v>0</v>
-      </c>
-      <c r="AU35" s="22"/>
-      <c r="AV35" s="22"/>
-      <c r="AW35" s="20"/>
-      <c r="AX35" s="22"/>
-      <c r="AY35" s="22"/>
-      <c r="AZ35" s="22"/>
-      <c r="BA35" s="22"/>
-      <c r="BB35" s="22"/>
-      <c r="BC35" s="22"/>
-      <c r="BD35" s="22"/>
-      <c r="BE35" s="22"/>
-      <c r="BF35" s="22"/>
-      <c r="BG35" s="22"/>
-      <c r="BH35" s="22"/>
-      <c r="BI35" s="22"/>
-      <c r="BJ35" s="22"/>
-      <c r="BK35" s="22"/>
-      <c r="BL35" s="22"/>
-      <c r="BM35" s="22"/>
-      <c r="BN35" s="22"/>
-      <c r="BO35" s="22"/>
-      <c r="BP35" s="22"/>
-      <c r="BQ35" s="22"/>
-      <c r="BR35" s="22"/>
-      <c r="BS35" s="22">
-        <v>5.7</v>
-      </c>
-      <c r="BT35" s="22"/>
-      <c r="BU35" s="22"/>
-      <c r="BV35" s="22"/>
-      <c r="BW35" s="22"/>
-      <c r="BX35" s="22"/>
-      <c r="BY35" s="22"/>
-      <c r="BZ35" s="22"/>
-      <c r="CA35" s="22"/>
-      <c r="CB35" s="22"/>
-      <c r="CC35" s="22"/>
-      <c r="CD35" s="22"/>
-      <c r="CE35" s="22"/>
-      <c r="CF35" s="22"/>
-      <c r="CG35" s="22"/>
-      <c r="CH35" s="22"/>
-      <c r="CI35" s="22"/>
-      <c r="CJ35" s="22"/>
-      <c r="CK35" s="22"/>
-      <c r="CL35" s="22"/>
-      <c r="CM35" s="22"/>
-      <c r="CN35" s="23"/>
-      <c r="CO35" s="23"/>
-      <c r="CP35" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ35" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR35" s="22">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="18.1322" customHeight="1">
-      <c r="A36" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" s="21">
-        <v>46203</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="E36" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F36" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G36" s="20" t="s">
-        <v>357</v>
-      </c>
-      <c r="H36" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="I36" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="J36" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="K36" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="L36" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="M36" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="N36" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="O36" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="P36" s="20"/>
-      <c r="Q36" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="R36" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="S36" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="T36" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="U36" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="V36" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="W36" s="20"/>
-      <c r="X36" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y36" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z36" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA36" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="AB36" s="20"/>
-      <c r="AC36" s="22">
-        <v>5</v>
-      </c>
-      <c r="AD36" s="22">
-        <v>50</v>
-      </c>
-      <c r="AE36" s="22">
-        <v>50</v>
-      </c>
-      <c r="AF36" s="22">
-        <v>0</v>
-      </c>
-      <c r="AG36" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="22"/>
-      <c r="AI36" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ36" s="22">
-        <v>0</v>
-      </c>
-      <c r="AK36" s="20"/>
-      <c r="AL36" s="22">
-        <v>38.55</v>
-      </c>
-      <c r="AM36" s="22">
-        <v>5.7</v>
-      </c>
-      <c r="AN36" s="22">
-        <v>44.25</v>
-      </c>
-      <c r="AO36" s="22">
-        <v>6.59</v>
-      </c>
-      <c r="AP36" s="22">
-        <v>2.6</v>
-      </c>
-      <c r="AQ36" s="22">
-        <v>10.69</v>
-      </c>
-      <c r="AR36" s="22">
-        <v>64.13</v>
-      </c>
-      <c r="AS36" s="22"/>
-      <c r="AT36" s="22">
-        <v>0</v>
-      </c>
-      <c r="AU36" s="22"/>
-      <c r="AV36" s="22"/>
-      <c r="AW36" s="20"/>
-      <c r="AX36" s="22"/>
-      <c r="AY36" s="22"/>
-      <c r="AZ36" s="22"/>
-      <c r="BA36" s="22"/>
-      <c r="BB36" s="22"/>
-      <c r="BC36" s="22"/>
-      <c r="BD36" s="22"/>
-      <c r="BE36" s="22"/>
-      <c r="BF36" s="22"/>
-      <c r="BG36" s="22"/>
-      <c r="BH36" s="22"/>
-      <c r="BI36" s="22"/>
-      <c r="BJ36" s="22"/>
-      <c r="BK36" s="22"/>
-      <c r="BL36" s="22"/>
-      <c r="BM36" s="22"/>
-      <c r="BN36" s="22"/>
-      <c r="BO36" s="22"/>
-      <c r="BP36" s="22"/>
-      <c r="BQ36" s="22"/>
-      <c r="BR36" s="22"/>
-      <c r="BS36" s="22">
-        <v>5.7</v>
-      </c>
-      <c r="BT36" s="22"/>
-      <c r="BU36" s="22"/>
-      <c r="BV36" s="22"/>
-      <c r="BW36" s="22"/>
-      <c r="BX36" s="22"/>
-      <c r="BY36" s="22"/>
-      <c r="BZ36" s="22"/>
-      <c r="CA36" s="22"/>
-      <c r="CB36" s="22"/>
-      <c r="CC36" s="22"/>
-      <c r="CD36" s="22"/>
-      <c r="CE36" s="22"/>
-      <c r="CF36" s="22"/>
-      <c r="CG36" s="22"/>
-      <c r="CH36" s="22"/>
-      <c r="CI36" s="22"/>
-      <c r="CJ36" s="22"/>
-      <c r="CK36" s="22"/>
-      <c r="CL36" s="22"/>
-      <c r="CM36" s="22"/>
-      <c r="CN36" s="22"/>
-      <c r="CO36" s="22"/>
-      <c r="CP36" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ36" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR36" s="22">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" ht="18.1322" customHeight="1">
-      <c r="A37" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" s="21">
-        <v>46203</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20" t="s">
-        <v>361</v>
-      </c>
-      <c r="J37" s="20" t="s">
-        <v>362</v>
-      </c>
-      <c r="K37" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="L37" s="20"/>
-      <c r="M37" s="20"/>
-      <c r="N37" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="O37" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="P37" s="20"/>
-      <c r="Q37" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="R37" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="S37" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="T37" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="U37" s="20" t="s">
-        <v>363</v>
-      </c>
-      <c r="V37" s="20" t="s">
-        <v>364</v>
-      </c>
-      <c r="W37" s="20" t="s">
-        <v>365</v>
-      </c>
-      <c r="X37" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y37" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="Z37" s="20" t="s">
-        <v>366</v>
-      </c>
-      <c r="AA37" s="20" t="s">
-        <v>367</v>
-      </c>
-      <c r="AB37" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="AC37" s="22">
-        <v>4</v>
-      </c>
-      <c r="AD37" s="22">
-        <v>19</v>
-      </c>
-      <c r="AE37" s="22">
-        <v>19</v>
-      </c>
-      <c r="AF37" s="22">
-        <v>0</v>
-      </c>
-      <c r="AG37" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH37" s="22"/>
-      <c r="AI37" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ37" s="22">
-        <v>0</v>
-      </c>
-      <c r="AK37" s="20"/>
-      <c r="AL37" s="22">
-        <v>23.16</v>
-      </c>
-      <c r="AM37" s="22">
-        <v>14.4</v>
-      </c>
-      <c r="AN37" s="22">
-        <v>37.56</v>
-      </c>
-      <c r="AO37" s="22">
-        <v>3.96</v>
-      </c>
-      <c r="AP37" s="22">
-        <v>2.6</v>
-      </c>
-      <c r="AQ37" s="22">
-        <v>8.82</v>
-      </c>
-      <c r="AR37" s="22">
-        <v>52.94</v>
-      </c>
-      <c r="AS37" s="22"/>
-      <c r="AT37" s="22">
-        <v>0</v>
-      </c>
-      <c r="AU37" s="22"/>
-      <c r="AV37" s="22"/>
-      <c r="AW37" s="20"/>
-      <c r="AX37" s="22"/>
-      <c r="AY37" s="22"/>
-      <c r="AZ37" s="22"/>
-      <c r="BA37" s="22"/>
-      <c r="BB37" s="22"/>
-      <c r="BC37" s="22"/>
-      <c r="BD37" s="22"/>
-      <c r="BE37" s="22"/>
-      <c r="BF37" s="22">
-        <v>9.9</v>
-      </c>
-      <c r="BG37" s="22"/>
-      <c r="BH37" s="22"/>
-      <c r="BI37" s="22"/>
-      <c r="BJ37" s="22"/>
-      <c r="BK37" s="22">
-        <v>4.5</v>
-      </c>
-      <c r="BL37" s="22"/>
-      <c r="BM37" s="22"/>
-      <c r="BN37" s="22"/>
-      <c r="BO37" s="22"/>
-      <c r="BP37" s="22"/>
-      <c r="BQ37" s="22"/>
-      <c r="BR37" s="22"/>
-      <c r="BS37" s="22"/>
-      <c r="BT37" s="22"/>
-      <c r="BU37" s="22"/>
-      <c r="BV37" s="22"/>
-      <c r="BW37" s="22"/>
-      <c r="BX37" s="22"/>
-      <c r="BY37" s="22"/>
-      <c r="BZ37" s="22"/>
-      <c r="CA37" s="22"/>
-      <c r="CB37" s="22"/>
-      <c r="CC37" s="22"/>
-      <c r="CD37" s="22"/>
-      <c r="CE37" s="22"/>
-      <c r="CF37" s="22"/>
-      <c r="CG37" s="22"/>
-      <c r="CH37" s="22"/>
-      <c r="CI37" s="22"/>
-      <c r="CJ37" s="22"/>
-      <c r="CK37" s="22"/>
-      <c r="CL37" s="22"/>
-      <c r="CM37" s="22"/>
-      <c r="CN37" s="23"/>
-      <c r="CO37" s="23"/>
-      <c r="CP37" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ37" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR37" s="22">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="18.1322" customHeight="1">
-      <c r="A38" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" s="21">
-        <v>46203</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="E38" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F38" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G38" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20" t="s">
-        <v>369</v>
-      </c>
-      <c r="J38" s="20" t="s">
-        <v>362</v>
-      </c>
-      <c r="K38" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="L38" s="20"/>
-      <c r="M38" s="20"/>
-      <c r="N38" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="O38" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="P38" s="20"/>
-      <c r="Q38" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="R38" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="S38" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="T38" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="U38" s="20" t="s">
-        <v>370</v>
-      </c>
-      <c r="V38" s="20" t="s">
-        <v>371</v>
-      </c>
-      <c r="W38" s="20" t="s">
-        <v>372</v>
-      </c>
-      <c r="X38" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y38" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="Z38" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="AA38" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="AB38" s="20"/>
-      <c r="AC38" s="22">
-        <v>1</v>
-      </c>
-      <c r="AD38" s="22">
-        <v>90</v>
-      </c>
-      <c r="AE38" s="22">
-        <v>90</v>
-      </c>
-      <c r="AF38" s="22">
-        <v>0</v>
-      </c>
-      <c r="AG38" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="22"/>
-      <c r="AI38" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ38" s="22">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="20"/>
-      <c r="AL38" s="22">
-        <v>209.42</v>
-      </c>
-      <c r="AM38" s="22">
-        <v>179.9</v>
-      </c>
-      <c r="AN38" s="22">
-        <v>389.32</v>
-      </c>
-      <c r="AO38" s="22">
-        <v>35.81</v>
-      </c>
-      <c r="AP38" s="22">
-        <v>2.6</v>
-      </c>
-      <c r="AQ38" s="22">
-        <v>85.54</v>
-      </c>
-      <c r="AR38" s="22">
-        <v>513.27</v>
-      </c>
-      <c r="AS38" s="22"/>
-      <c r="AT38" s="22">
-        <v>0</v>
-      </c>
-      <c r="AU38" s="22"/>
-      <c r="AV38" s="22"/>
-      <c r="AW38" s="20"/>
-      <c r="AX38" s="22"/>
-      <c r="AY38" s="22">
-        <v>170</v>
-      </c>
-      <c r="AZ38" s="22"/>
-      <c r="BA38" s="22"/>
-      <c r="BB38" s="22"/>
-      <c r="BC38" s="22"/>
-      <c r="BD38" s="22"/>
-      <c r="BE38" s="22"/>
-      <c r="BF38" s="22">
-        <v>9.9</v>
-      </c>
-      <c r="BG38" s="22"/>
-      <c r="BH38" s="22"/>
-      <c r="BI38" s="22"/>
-      <c r="BJ38" s="22"/>
-      <c r="BK38" s="22"/>
-      <c r="BL38" s="22"/>
-      <c r="BM38" s="22"/>
-      <c r="BN38" s="22"/>
-      <c r="BO38" s="22"/>
-      <c r="BP38" s="22"/>
-      <c r="BQ38" s="22"/>
-      <c r="BR38" s="22"/>
-      <c r="BS38" s="22"/>
-      <c r="BT38" s="22"/>
-      <c r="BU38" s="22"/>
-      <c r="BV38" s="22"/>
-      <c r="BW38" s="22"/>
-      <c r="BX38" s="22"/>
-      <c r="BY38" s="22"/>
-      <c r="BZ38" s="22"/>
-      <c r="CA38" s="22"/>
-      <c r="CB38" s="22"/>
-      <c r="CC38" s="22"/>
-      <c r="CD38" s="22"/>
-      <c r="CE38" s="22"/>
-      <c r="CF38" s="22"/>
-      <c r="CG38" s="22"/>
-      <c r="CH38" s="22"/>
-      <c r="CI38" s="22"/>
-      <c r="CJ38" s="22"/>
-      <c r="CK38" s="22"/>
-      <c r="CL38" s="22"/>
-      <c r="CM38" s="22"/>
-      <c r="CN38" s="22"/>
-      <c r="CO38" s="22"/>
-      <c r="CP38" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ38" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR38" s="22">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" ht="18.1322" customHeight="1">
-      <c r="A39" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" s="21">
-        <v>46203</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G39" s="20" t="s">
-        <v>373</v>
-      </c>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20" t="s">
-        <v>374</v>
-      </c>
-      <c r="J39" s="20" t="s">
-        <v>362</v>
-      </c>
-      <c r="K39" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="L39" s="20"/>
-      <c r="M39" s="20"/>
-      <c r="N39" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="O39" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="P39" s="20"/>
-      <c r="Q39" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="R39" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="S39" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="T39" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="U39" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="V39" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="W39" s="20"/>
-      <c r="X39" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y39" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z39" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="AA39" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="AB39" s="20"/>
-      <c r="AC39" s="22">
-        <v>1</v>
-      </c>
-      <c r="AD39" s="22">
-        <v>35.5</v>
-      </c>
-      <c r="AE39" s="22">
-        <v>35.5</v>
-      </c>
-      <c r="AF39" s="22">
-        <v>0</v>
-      </c>
-      <c r="AG39" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH39" s="22"/>
-      <c r="AI39" s="22">
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="22">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="20"/>
-      <c r="AL39" s="22">
-        <v>36.01</v>
-      </c>
-      <c r="AM39" s="22"/>
-      <c r="AN39" s="22">
-        <v>36.01</v>
-      </c>
-      <c r="AO39" s="22">
-        <v>6.16</v>
-      </c>
-      <c r="AP39" s="22">
-        <v>2.6</v>
-      </c>
-      <c r="AQ39" s="22">
-        <v>8.95</v>
-      </c>
-      <c r="AR39" s="22">
-        <v>53.72</v>
-      </c>
-      <c r="AS39" s="22"/>
-      <c r="AT39" s="22">
-        <v>0</v>
-      </c>
-      <c r="AU39" s="22"/>
-      <c r="AV39" s="22"/>
-      <c r="AW39" s="20"/>
-      <c r="AX39" s="22"/>
-      <c r="AY39" s="22"/>
-      <c r="AZ39" s="22"/>
-      <c r="BA39" s="22"/>
-      <c r="BB39" s="22"/>
-      <c r="BC39" s="22"/>
-      <c r="BD39" s="22"/>
-      <c r="BE39" s="22"/>
-      <c r="BF39" s="22"/>
-      <c r="BG39" s="22"/>
-      <c r="BH39" s="22"/>
-      <c r="BI39" s="22"/>
-      <c r="BJ39" s="22"/>
-      <c r="BK39" s="22"/>
-      <c r="BL39" s="22"/>
-      <c r="BM39" s="22"/>
-      <c r="BN39" s="22"/>
-      <c r="BO39" s="22"/>
-      <c r="BP39" s="22"/>
-      <c r="BQ39" s="22"/>
-      <c r="BR39" s="22"/>
-      <c r="BS39" s="22"/>
-      <c r="BT39" s="22"/>
-      <c r="BU39" s="22"/>
-      <c r="BV39" s="22"/>
-      <c r="BW39" s="22"/>
-      <c r="BX39" s="22"/>
-      <c r="BY39" s="22"/>
-      <c r="BZ39" s="22"/>
-      <c r="CA39" s="22"/>
-      <c r="CB39" s="22"/>
-      <c r="CC39" s="22"/>
-      <c r="CD39" s="22"/>
-      <c r="CE39" s="22"/>
-      <c r="CF39" s="22"/>
-      <c r="CG39" s="22"/>
-      <c r="CH39" s="22"/>
-      <c r="CI39" s="22"/>
-      <c r="CJ39" s="22"/>
-      <c r="CK39" s="22"/>
-      <c r="CL39" s="22"/>
-      <c r="CM39" s="22"/>
-      <c r="CN39" s="23"/>
-      <c r="CO39" s="23"/>
-      <c r="CP39" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CQ39" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="CR39" s="22">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
+    <row r="33" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:AK3"/>
     <mergeCell ref="AL3:AR3"/>
     <mergeCell ref="AS3:CM3"/>
     <mergeCell ref="C1:CM1"/>
-    <mergeCell ref="CN3:CO3"/>
-    <mergeCell ref="CP3:CQ3"/>
+    <mergeCell ref="CO3:CP3"/>
   </mergeCells>
   <pageSetup paperSize="9" scale="100" orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
@@ -8647,7 +7219,7 @@
       <c r="A1" s="24"/>
       <c r="B1" s="24"/>
       <c r="C1" s="25" t="s">
-        <v>375</v>
+        <v>340</v>
       </c>
       <c r="D1" s="25"/>
       <c r="E1" s="25"/>
@@ -8683,22 +7255,22 @@
         <v>28</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>376</v>
+        <v>341</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>377</v>
+        <v>342</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>378</v>
+        <v>343</v>
       </c>
       <c r="H3" s="19" t="s">
         <v>65</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>379</v>
+        <v>344</v>
       </c>
       <c r="J3" s="19" t="s">
-        <v>380</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="18.1322" customHeight="1">
@@ -8706,23 +7278,23 @@
         <v>15</v>
       </c>
       <c r="B4" s="27">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="28">
-        <v>619.6</v>
+        <v>441.23</v>
       </c>
       <c r="F4" s="28"/>
       <c r="G4" s="28">
-        <v>91.76</v>
+        <v>180.37</v>
       </c>
       <c r="H4" s="28">
-        <v>88.4</v>
+        <v>65</v>
       </c>
       <c r="I4" s="28"/>
       <c r="J4" s="28">
